--- a/pocos/public/invoice-template.xlsx
+++ b/pocos/public/invoice-template.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="209">
   <si>
     <t>주식회사 제이더블유엘컴퍼니</t>
   </si>
@@ -154,9 +154,6 @@
   </si>
   <si>
     <t>만근수당</t>
-  </si>
-  <si>
-    <t>교통비</t>
   </si>
   <si>
     <t xml:space="preserve">직접비
@@ -2478,7 +2475,7 @@
     <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3444,7 +3441,7 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A1" s="154" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B1" s="154"/>
       <c r="C1" s="154"/>
@@ -3649,13 +3646,13 @@
         <v>36</v>
       </c>
       <c r="C5" s="159" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D5" s="160" t="s">
         <v>37</v>
       </c>
       <c r="E5" s="161" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F5" s="162">
         <v>1</v>
@@ -3751,10 +3748,10 @@
         <v>31</v>
       </c>
       <c r="AK5" s="168" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL5" s="169" t="s">
         <v>197</v>
-      </c>
-      <c r="AL5" s="169" t="s">
-        <v>198</v>
       </c>
       <c r="AM5" s="60" t="s">
         <v>33</v>
@@ -3773,88 +3770,88 @@
       <c r="D6" s="173"/>
       <c r="E6" s="174"/>
       <c r="F6" s="175" t="s">
+        <v>198</v>
+      </c>
+      <c r="G6" s="176" t="s">
         <v>199</v>
       </c>
-      <c r="G6" s="176" t="s">
+      <c r="H6" s="176" t="s">
         <v>200</v>
       </c>
-      <c r="H6" s="176" t="s">
+      <c r="I6" s="176" t="s">
         <v>201</v>
       </c>
-      <c r="I6" s="176" t="s">
+      <c r="J6" s="176" t="s">
         <v>202</v>
       </c>
-      <c r="J6" s="176" t="s">
+      <c r="K6" s="176" t="s">
         <v>203</v>
       </c>
-      <c r="K6" s="176" t="s">
+      <c r="L6" s="177" t="s">
         <v>204</v>
       </c>
-      <c r="L6" s="177" t="s">
-        <v>205</v>
-      </c>
       <c r="M6" s="178" t="s">
+        <v>198</v>
+      </c>
+      <c r="N6" s="176" t="s">
         <v>199</v>
       </c>
-      <c r="N6" s="176" t="s">
+      <c r="O6" s="176" t="s">
         <v>200</v>
       </c>
-      <c r="O6" s="176" t="s">
+      <c r="P6" s="176" t="s">
         <v>201</v>
       </c>
-      <c r="P6" s="176" t="s">
+      <c r="Q6" s="176" t="s">
         <v>202</v>
       </c>
-      <c r="Q6" s="176" t="s">
+      <c r="R6" s="176" t="s">
         <v>203</v>
       </c>
-      <c r="R6" s="176" t="s">
+      <c r="S6" s="177" t="s">
         <v>204</v>
       </c>
-      <c r="S6" s="177" t="s">
-        <v>205</v>
-      </c>
       <c r="T6" s="178" t="s">
+        <v>198</v>
+      </c>
+      <c r="U6" s="178" t="s">
         <v>199</v>
       </c>
-      <c r="U6" s="178" t="s">
+      <c r="V6" s="178" t="s">
         <v>200</v>
       </c>
-      <c r="V6" s="178" t="s">
+      <c r="W6" s="178" t="s">
         <v>201</v>
       </c>
-      <c r="W6" s="178" t="s">
+      <c r="X6" s="176" t="s">
         <v>202</v>
       </c>
-      <c r="X6" s="176" t="s">
+      <c r="Y6" s="176" t="s">
         <v>203</v>
       </c>
-      <c r="Y6" s="176" t="s">
+      <c r="Z6" s="177" t="s">
         <v>204</v>
       </c>
-      <c r="Z6" s="177" t="s">
-        <v>205</v>
-      </c>
       <c r="AA6" s="178" t="s">
+        <v>198</v>
+      </c>
+      <c r="AB6" s="176" t="s">
         <v>199</v>
       </c>
-      <c r="AB6" s="176" t="s">
+      <c r="AC6" s="176" t="s">
         <v>200</v>
       </c>
-      <c r="AC6" s="176" t="s">
+      <c r="AD6" s="176" t="s">
         <v>201</v>
       </c>
-      <c r="AD6" s="176" t="s">
+      <c r="AE6" s="176" t="s">
         <v>202</v>
       </c>
-      <c r="AE6" s="176" t="s">
+      <c r="AF6" s="176" t="s">
         <v>203</v>
       </c>
-      <c r="AF6" s="176" t="s">
+      <c r="AG6" s="177" t="s">
         <v>204</v>
-      </c>
-      <c r="AG6" s="177" t="s">
-        <v>205</v>
       </c>
       <c r="AH6" s="179"/>
       <c r="AI6" s="179"/>
@@ -3871,7 +3868,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="159" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7" s="159" t="s">
         <v>28</v>
@@ -3880,7 +3877,7 @@
         <v>10450</v>
       </c>
       <c r="E7" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F7" s="186">
         <v>8</v>
@@ -4036,7 +4033,7 @@
       <c r="C9" s="172"/>
       <c r="D9" s="197"/>
       <c r="E9" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F9" s="199"/>
       <c r="G9" s="200"/>
@@ -4170,7 +4167,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="159" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C12" s="220" t="s">
         <v>32</v>
@@ -4179,7 +4176,7 @@
         <v>10450</v>
       </c>
       <c r="E12" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F12" s="186">
         <v>8</v>
@@ -4339,7 +4336,7 @@
       <c r="C14" s="224"/>
       <c r="D14" s="197"/>
       <c r="E14" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F14" s="199"/>
       <c r="G14" s="200"/>
@@ -4479,7 +4476,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="172" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C17" s="172" t="s">
         <v>28</v>
@@ -4488,7 +4485,7 @@
         <v>10450</v>
       </c>
       <c r="E17" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F17" s="186">
         <v>8</v>
@@ -4656,7 +4653,7 @@
       <c r="C19" s="172"/>
       <c r="D19" s="197"/>
       <c r="E19" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F19" s="199"/>
       <c r="G19" s="200"/>
@@ -4794,7 +4791,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="159" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C22" s="220" t="s">
         <v>32</v>
@@ -4803,7 +4800,7 @@
         <v>10450</v>
       </c>
       <c r="E22" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F22" s="186">
         <v>8</v>
@@ -4963,7 +4960,7 @@
       <c r="C24" s="224"/>
       <c r="D24" s="197"/>
       <c r="E24" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F24" s="199"/>
       <c r="G24" s="200"/>
@@ -5097,7 +5094,7 @@
         <v>5</v>
       </c>
       <c r="B27" s="172" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C27" s="172" t="s">
         <v>28</v>
@@ -5106,7 +5103,7 @@
         <v>10450</v>
       </c>
       <c r="E27" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F27" s="186">
         <v>8</v>
@@ -5260,7 +5257,7 @@
       <c r="C29" s="172"/>
       <c r="D29" s="197"/>
       <c r="E29" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F29" s="199"/>
       <c r="G29" s="200"/>
@@ -5394,7 +5391,7 @@
         <v>6</v>
       </c>
       <c r="B32" s="159" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C32" s="220" t="s">
         <v>32</v>
@@ -5403,7 +5400,7 @@
         <v>10450</v>
       </c>
       <c r="E32" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F32" s="186">
         <v>8</v>
@@ -5555,7 +5552,7 @@
       <c r="C34" s="224"/>
       <c r="D34" s="197"/>
       <c r="E34" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F34" s="199"/>
       <c r="G34" s="200"/>
@@ -5689,7 +5686,7 @@
         <v>7</v>
       </c>
       <c r="B37" s="172" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C37" s="220" t="s">
         <v>32</v>
@@ -5698,7 +5695,7 @@
         <v>10450</v>
       </c>
       <c r="E37" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F37" s="186">
         <v>8</v>
@@ -5866,7 +5863,7 @@
       <c r="C39" s="224"/>
       <c r="D39" s="197"/>
       <c r="E39" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F39" s="199"/>
       <c r="G39" s="200"/>
@@ -6004,7 +6001,7 @@
         <v>8</v>
       </c>
       <c r="B42" s="159" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C42" s="159" t="s">
         <v>28</v>
@@ -6013,7 +6010,7 @@
         <v>10450</v>
       </c>
       <c r="E42" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F42" s="186">
         <v>8</v>
@@ -6171,7 +6168,7 @@
       <c r="C44" s="172"/>
       <c r="D44" s="197"/>
       <c r="E44" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F44" s="199"/>
       <c r="G44" s="200"/>
@@ -6311,7 +6308,7 @@
         <v>9</v>
       </c>
       <c r="B47" s="172" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C47" s="224" t="s">
         <v>32</v>
@@ -6320,7 +6317,7 @@
         <v>10450</v>
       </c>
       <c r="E47" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F47" s="186">
         <v>8</v>
@@ -6470,7 +6467,7 @@
       <c r="C49" s="224"/>
       <c r="D49" s="197"/>
       <c r="E49" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F49" s="199"/>
       <c r="G49" s="200"/>
@@ -6606,7 +6603,7 @@
         <v>10</v>
       </c>
       <c r="B52" s="159" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C52" s="220" t="s">
         <v>32</v>
@@ -6615,7 +6612,7 @@
         <v>10450</v>
       </c>
       <c r="E52" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F52" s="186">
         <v>8</v>
@@ -6785,7 +6782,7 @@
       <c r="C54" s="224"/>
       <c r="D54" s="197"/>
       <c r="E54" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F54" s="199"/>
       <c r="G54" s="200"/>
@@ -6919,7 +6916,7 @@
         <v>11</v>
       </c>
       <c r="B57" s="172" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C57" s="172" t="s">
         <v>28</v>
@@ -6928,7 +6925,7 @@
         <v>10450</v>
       </c>
       <c r="E57" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F57" s="186">
         <v>8</v>
@@ -7082,7 +7079,7 @@
       <c r="C59" s="172"/>
       <c r="D59" s="197"/>
       <c r="E59" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F59" s="199"/>
       <c r="G59" s="200"/>
@@ -7216,7 +7213,7 @@
         <v>12</v>
       </c>
       <c r="B62" s="159" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C62" s="159" t="s">
         <v>28</v>
@@ -7225,7 +7222,7 @@
         <v>10450</v>
       </c>
       <c r="E62" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F62" s="186">
         <v>8</v>
@@ -7379,7 +7376,7 @@
       <c r="C64" s="172"/>
       <c r="D64" s="197"/>
       <c r="E64" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F64" s="199"/>
       <c r="G64" s="200"/>
@@ -7519,7 +7516,7 @@
         <v>13</v>
       </c>
       <c r="B67" s="159" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C67" s="159" t="s">
         <v>28</v>
@@ -7528,7 +7525,7 @@
         <v>10450</v>
       </c>
       <c r="E67" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F67" s="186">
         <v>8</v>
@@ -7696,7 +7693,7 @@
       <c r="C69" s="172"/>
       <c r="D69" s="197"/>
       <c r="E69" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F69" s="199"/>
       <c r="G69" s="200"/>
@@ -7830,7 +7827,7 @@
         <v>14</v>
       </c>
       <c r="B72" s="159" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C72" s="159" t="s">
         <v>28</v>
@@ -7839,7 +7836,7 @@
         <v>10450</v>
       </c>
       <c r="E72" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F72" s="186">
         <v>8</v>
@@ -7997,7 +7994,7 @@
       <c r="C74" s="172"/>
       <c r="D74" s="197"/>
       <c r="E74" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F74" s="199"/>
       <c r="G74" s="200"/>
@@ -8010,13 +8007,13 @@
       <c r="N74" s="200"/>
       <c r="O74" s="200"/>
       <c r="P74" s="203" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q74" s="203" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="R74" s="203" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S74" s="201"/>
       <c r="T74" s="202"/>
@@ -8061,13 +8058,13 @@
       <c r="N75" s="200"/>
       <c r="O75" s="200"/>
       <c r="P75" s="203" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q75" s="203" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="R75" s="203" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="S75" s="201"/>
       <c r="T75" s="202"/>
@@ -8143,7 +8140,7 @@
         <v>15</v>
       </c>
       <c r="B77" s="172" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C77" s="172" t="s">
         <v>28</v>
@@ -8152,7 +8149,7 @@
         <v>10450</v>
       </c>
       <c r="E77" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F77" s="186">
         <v>8</v>
@@ -8318,7 +8315,7 @@
       <c r="C79" s="172"/>
       <c r="D79" s="197"/>
       <c r="E79" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F79" s="199"/>
       <c r="G79" s="200"/>
@@ -8456,7 +8453,7 @@
         <v>16</v>
       </c>
       <c r="B82" s="159" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C82" s="159" t="s">
         <v>28</v>
@@ -8465,7 +8462,7 @@
         <v>10450</v>
       </c>
       <c r="E82" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F82" s="186">
         <v>8</v>
@@ -8623,7 +8620,7 @@
       <c r="C84" s="172"/>
       <c r="D84" s="197"/>
       <c r="E84" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F84" s="199"/>
       <c r="G84" s="200"/>
@@ -8757,7 +8754,7 @@
         <v>17</v>
       </c>
       <c r="B87" s="159" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C87" s="159" t="s">
         <v>28</v>
@@ -8766,7 +8763,7 @@
         <v>10450</v>
       </c>
       <c r="E87" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F87" s="186">
         <v>8</v>
@@ -8918,7 +8915,7 @@
       <c r="C89" s="172"/>
       <c r="D89" s="197"/>
       <c r="E89" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F89" s="199"/>
       <c r="G89" s="200"/>
@@ -9052,7 +9049,7 @@
         <v>18</v>
       </c>
       <c r="B92" s="172" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C92" s="172" t="s">
         <v>28</v>
@@ -9061,7 +9058,7 @@
         <v>10450</v>
       </c>
       <c r="E92" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F92" s="186">
         <v>8</v>
@@ -9219,7 +9216,7 @@
       <c r="C94" s="172"/>
       <c r="D94" s="197"/>
       <c r="E94" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F94" s="199"/>
       <c r="G94" s="200"/>
@@ -9353,7 +9350,7 @@
         <v>19</v>
       </c>
       <c r="B97" s="159" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C97" s="220" t="s">
         <v>32</v>
@@ -9362,7 +9359,7 @@
         <v>10450</v>
       </c>
       <c r="E97" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F97" s="186">
         <v>8</v>
@@ -9512,7 +9509,7 @@
       <c r="C99" s="224"/>
       <c r="D99" s="197"/>
       <c r="E99" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F99" s="199"/>
       <c r="G99" s="200"/>
@@ -9646,7 +9643,7 @@
         <v>20</v>
       </c>
       <c r="B102" s="172" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C102" s="172" t="s">
         <v>28</v>
@@ -9655,7 +9652,7 @@
         <v>10450</v>
       </c>
       <c r="E102" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F102" s="186">
         <v>8</v>
@@ -9809,7 +9806,7 @@
       <c r="C104" s="172"/>
       <c r="D104" s="197"/>
       <c r="E104" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F104" s="199"/>
       <c r="G104" s="200"/>
@@ -9943,7 +9940,7 @@
         <v>21</v>
       </c>
       <c r="B107" s="159" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C107" s="159" t="s">
         <v>28</v>
@@ -9952,7 +9949,7 @@
         <v>10450</v>
       </c>
       <c r="E107" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F107" s="186">
         <v>8</v>
@@ -10106,7 +10103,7 @@
       <c r="C109" s="172"/>
       <c r="D109" s="197"/>
       <c r="E109" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F109" s="199"/>
       <c r="G109" s="200"/>
@@ -10244,7 +10241,7 @@
         <v>22</v>
       </c>
       <c r="B112" s="172" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C112" s="172" t="s">
         <v>28</v>
@@ -10253,7 +10250,7 @@
         <v>10450</v>
       </c>
       <c r="E112" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F112" s="186">
         <v>8</v>
@@ -10423,7 +10420,7 @@
       <c r="C114" s="172"/>
       <c r="D114" s="197"/>
       <c r="E114" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F114" s="199"/>
       <c r="G114" s="200"/>
@@ -10565,7 +10562,7 @@
         <v>23</v>
       </c>
       <c r="B117" s="159" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C117" s="159" t="s">
         <v>28</v>
@@ -10574,7 +10571,7 @@
         <v>10450</v>
       </c>
       <c r="E117" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F117" s="186">
         <v>8</v>
@@ -10718,7 +10715,7 @@
       <c r="C119" s="172"/>
       <c r="D119" s="197"/>
       <c r="E119" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F119" s="199"/>
       <c r="G119" s="200"/>
@@ -10852,7 +10849,7 @@
         <v>24</v>
       </c>
       <c r="B122" s="172" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C122" s="172" t="s">
         <v>28</v>
@@ -10861,7 +10858,7 @@
         <v>10450</v>
       </c>
       <c r="E122" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F122" s="186">
         <v>8</v>
@@ -11029,7 +11026,7 @@
       <c r="C124" s="172"/>
       <c r="D124" s="197"/>
       <c r="E124" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F124" s="199"/>
       <c r="G124" s="203"/>
@@ -11173,7 +11170,7 @@
         <v>25</v>
       </c>
       <c r="B127" s="159" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C127" s="159" t="s">
         <v>28</v>
@@ -11182,7 +11179,7 @@
         <v>10450</v>
       </c>
       <c r="E127" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F127" s="186">
         <v>8</v>
@@ -11316,7 +11313,7 @@
       <c r="C129" s="172"/>
       <c r="D129" s="197"/>
       <c r="E129" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F129" s="199"/>
       <c r="G129" s="200"/>
@@ -11450,7 +11447,7 @@
         <v>26</v>
       </c>
       <c r="B132" s="159" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C132" s="159" t="s">
         <v>28</v>
@@ -11459,7 +11456,7 @@
         <v>10320</v>
       </c>
       <c r="E132" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F132" s="186">
         <v>8</v>
@@ -11625,7 +11622,7 @@
       <c r="C134" s="172"/>
       <c r="D134" s="248"/>
       <c r="E134" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F134" s="199"/>
       <c r="G134" s="200"/>
@@ -11759,7 +11756,7 @@
         <v>27</v>
       </c>
       <c r="B137" s="159" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C137" s="159" t="s">
         <v>28</v>
@@ -11768,7 +11765,7 @@
         <v>10320</v>
       </c>
       <c r="E137" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F137" s="186">
         <v>8</v>
@@ -11900,7 +11897,7 @@
       <c r="C139" s="172"/>
       <c r="D139" s="248"/>
       <c r="E139" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F139" s="199"/>
       <c r="G139" s="200"/>
@@ -12034,7 +12031,7 @@
         <v>28</v>
       </c>
       <c r="B142" s="159" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C142" s="159" t="s">
         <v>28</v>
@@ -12043,7 +12040,7 @@
         <v>10320</v>
       </c>
       <c r="E142" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F142" s="186"/>
       <c r="G142" s="244"/>
@@ -12181,7 +12178,7 @@
       <c r="C144" s="172"/>
       <c r="D144" s="248"/>
       <c r="E144" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F144" s="199"/>
       <c r="G144" s="245"/>
@@ -12315,7 +12312,7 @@
         <v>29</v>
       </c>
       <c r="B147" s="159" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C147" s="159" t="s">
         <v>28</v>
@@ -12324,7 +12321,7 @@
         <v>10320</v>
       </c>
       <c r="E147" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F147" s="186">
         <v>8</v>
@@ -12494,7 +12491,7 @@
       <c r="C149" s="172"/>
       <c r="D149" s="248"/>
       <c r="E149" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F149" s="199"/>
       <c r="G149" s="200"/>
@@ -12634,7 +12631,7 @@
         <v>30</v>
       </c>
       <c r="B152" s="159" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C152" s="159" t="s">
         <v>28</v>
@@ -12643,7 +12640,7 @@
         <v>10320</v>
       </c>
       <c r="E152" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F152" s="186">
         <v>8</v>
@@ -12795,7 +12792,7 @@
       <c r="C154" s="172"/>
       <c r="D154" s="248"/>
       <c r="E154" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F154" s="199"/>
       <c r="G154" s="200"/>
@@ -12929,7 +12926,7 @@
         <v>31</v>
       </c>
       <c r="B157" s="159" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C157" s="159" t="s">
         <v>28</v>
@@ -12938,7 +12935,7 @@
         <v>10320</v>
       </c>
       <c r="E157" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F157" s="186">
         <v>8</v>
@@ -13104,7 +13101,7 @@
       <c r="C159" s="172"/>
       <c r="D159" s="248"/>
       <c r="E159" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F159" s="199"/>
       <c r="G159" s="200"/>
@@ -13242,7 +13239,7 @@
         <v>32</v>
       </c>
       <c r="B162" s="159" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C162" s="159" t="s">
         <v>28</v>
@@ -13251,7 +13248,7 @@
         <v>10320</v>
       </c>
       <c r="E162" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F162" s="186">
         <v>8</v>
@@ -13405,7 +13402,7 @@
       <c r="C164" s="172"/>
       <c r="D164" s="248"/>
       <c r="E164" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F164" s="199"/>
       <c r="G164" s="200"/>
@@ -13543,7 +13540,7 @@
         <v>33</v>
       </c>
       <c r="B167" s="159" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C167" s="250" t="s">
         <v>33</v>
@@ -13552,7 +13549,7 @@
         <v>10320</v>
       </c>
       <c r="E167" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F167" s="186">
         <v>8</v>
@@ -13708,7 +13705,7 @@
       <c r="C169" s="250"/>
       <c r="D169" s="248"/>
       <c r="E169" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F169" s="199"/>
       <c r="G169" s="200"/>
@@ -13844,7 +13841,7 @@
         <v>34</v>
       </c>
       <c r="B172" s="159" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C172" s="250" t="s">
         <v>33</v>
@@ -13853,7 +13850,7 @@
         <v>10320</v>
       </c>
       <c r="E172" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F172" s="186">
         <v>8</v>
@@ -14001,7 +13998,7 @@
       <c r="C174" s="250"/>
       <c r="D174" s="248"/>
       <c r="E174" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F174" s="199"/>
       <c r="G174" s="200"/>
@@ -14137,7 +14134,7 @@
         <v>35</v>
       </c>
       <c r="B177" s="159" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C177" s="250" t="s">
         <v>33</v>
@@ -14146,7 +14143,7 @@
         <v>10320</v>
       </c>
       <c r="E177" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F177" s="186">
         <v>8</v>
@@ -14300,7 +14297,7 @@
       <c r="C179" s="250"/>
       <c r="D179" s="248"/>
       <c r="E179" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F179" s="199"/>
       <c r="G179" s="200"/>
@@ -14434,7 +14431,7 @@
         <v>36</v>
       </c>
       <c r="B182" s="159" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C182" s="250" t="s">
         <v>33</v>
@@ -14443,7 +14440,7 @@
         <v>10320</v>
       </c>
       <c r="E182" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F182" s="186"/>
       <c r="G182" s="187">
@@ -14575,7 +14572,7 @@
       <c r="C184" s="250"/>
       <c r="D184" s="248"/>
       <c r="E184" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F184" s="199"/>
       <c r="G184" s="200"/>
@@ -14709,7 +14706,7 @@
         <v>37</v>
       </c>
       <c r="B187" s="172" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C187" s="172" t="s">
         <v>28</v>
@@ -14718,7 +14715,7 @@
         <v>10320</v>
       </c>
       <c r="E187" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F187" s="186">
         <v>8</v>
@@ -14884,7 +14881,7 @@
       <c r="C189" s="172"/>
       <c r="D189" s="248"/>
       <c r="E189" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F189" s="199"/>
       <c r="G189" s="200"/>
@@ -15022,7 +15019,7 @@
         <v>38</v>
       </c>
       <c r="B192" s="159" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C192" s="159" t="s">
         <v>28</v>
@@ -15031,7 +15028,7 @@
         <v>10320</v>
       </c>
       <c r="E192" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F192" s="186">
         <v>8</v>
@@ -15183,7 +15180,7 @@
       <c r="C194" s="172"/>
       <c r="D194" s="248"/>
       <c r="E194" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F194" s="199"/>
       <c r="G194" s="200"/>
@@ -15317,7 +15314,7 @@
         <v>39</v>
       </c>
       <c r="B197" s="159" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C197" s="159" t="s">
         <v>28</v>
@@ -15326,7 +15323,7 @@
         <v>10320</v>
       </c>
       <c r="E197" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F197" s="186">
         <v>8</v>
@@ -15494,7 +15491,7 @@
       <c r="C199" s="172"/>
       <c r="D199" s="248"/>
       <c r="E199" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F199" s="199"/>
       <c r="G199" s="200"/>
@@ -15628,7 +15625,7 @@
         <v>40</v>
       </c>
       <c r="B202" s="172" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C202" s="172" t="s">
         <v>28</v>
@@ -15637,7 +15634,7 @@
         <v>10320</v>
       </c>
       <c r="E202" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F202" s="186">
         <v>8</v>
@@ -15795,7 +15792,7 @@
       <c r="C204" s="172"/>
       <c r="D204" s="248"/>
       <c r="E204" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F204" s="199"/>
       <c r="G204" s="200"/>
@@ -15935,7 +15932,7 @@
         <v>41</v>
       </c>
       <c r="B207" s="159" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C207" s="159" t="s">
         <v>28</v>
@@ -15944,7 +15941,7 @@
         <v>10320</v>
       </c>
       <c r="E207" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F207" s="186">
         <v>8</v>
@@ -16106,7 +16103,7 @@
       <c r="C209" s="172"/>
       <c r="D209" s="248"/>
       <c r="E209" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F209" s="199"/>
       <c r="G209" s="200"/>
@@ -16240,7 +16237,7 @@
         <v>42</v>
       </c>
       <c r="B212" s="159" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C212" s="159" t="s">
         <v>28</v>
@@ -16249,7 +16246,7 @@
         <v>10320</v>
       </c>
       <c r="E212" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F212" s="186">
         <v>8</v>
@@ -16419,7 +16416,7 @@
       <c r="C214" s="172"/>
       <c r="D214" s="248"/>
       <c r="E214" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F214" s="199"/>
       <c r="G214" s="200"/>
@@ -16561,7 +16558,7 @@
         <v>43</v>
       </c>
       <c r="B217" s="172" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C217" s="172" t="s">
         <v>28</v>
@@ -16570,7 +16567,7 @@
         <v>10320</v>
       </c>
       <c r="E217" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F217" s="186">
         <v>8</v>
@@ -16738,7 +16735,7 @@
       <c r="C219" s="172"/>
       <c r="D219" s="248"/>
       <c r="E219" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F219" s="199"/>
       <c r="G219" s="200"/>
@@ -16874,7 +16871,7 @@
         <v>44</v>
       </c>
       <c r="B222" s="159" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C222" s="159" t="s">
         <v>28</v>
@@ -16883,7 +16880,7 @@
         <v>10320</v>
       </c>
       <c r="E222" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F222" s="186">
         <v>8</v>
@@ -17045,7 +17042,7 @@
       <c r="C224" s="172"/>
       <c r="D224" s="248"/>
       <c r="E224" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F224" s="199"/>
       <c r="G224" s="200"/>
@@ -17181,7 +17178,7 @@
         <v>45</v>
       </c>
       <c r="B227" s="172" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C227" s="172" t="s">
         <v>28</v>
@@ -17190,7 +17187,7 @@
         <v>10320</v>
       </c>
       <c r="E227" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F227" s="186">
         <v>8</v>
@@ -17350,7 +17347,7 @@
       <c r="C229" s="172"/>
       <c r="D229" s="248"/>
       <c r="E229" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F229" s="199"/>
       <c r="G229" s="200"/>
@@ -17488,7 +17485,7 @@
         <v>46</v>
       </c>
       <c r="B232" s="159" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C232" s="159" t="s">
         <v>28</v>
@@ -17497,7 +17494,7 @@
         <v>10320</v>
       </c>
       <c r="E232" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F232" s="186">
         <v>8</v>
@@ -17641,7 +17638,7 @@
       <c r="C234" s="172"/>
       <c r="D234" s="248"/>
       <c r="E234" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F234" s="199"/>
       <c r="G234" s="200"/>
@@ -17775,7 +17772,7 @@
         <v>47</v>
       </c>
       <c r="B237" s="159" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C237" s="252" t="s">
         <v>33</v>
@@ -17784,7 +17781,7 @@
         <v>10320</v>
       </c>
       <c r="E237" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F237" s="186"/>
       <c r="G237" s="187">
@@ -17894,7 +17891,7 @@
       <c r="C239" s="250"/>
       <c r="D239" s="248"/>
       <c r="E239" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F239" s="199"/>
       <c r="G239" s="200"/>
@@ -18028,7 +18025,7 @@
         <v>48</v>
       </c>
       <c r="B242" s="159" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C242" s="159" t="s">
         <v>28</v>
@@ -18037,7 +18034,7 @@
         <v>10320</v>
       </c>
       <c r="E242" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F242" s="186">
         <v>8</v>
@@ -18197,7 +18194,7 @@
       <c r="C244" s="172"/>
       <c r="D244" s="248"/>
       <c r="E244" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F244" s="199"/>
       <c r="G244" s="200"/>
@@ -18337,7 +18334,7 @@
         <v>49</v>
       </c>
       <c r="B247" s="159" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C247" s="159" t="s">
         <v>28</v>
@@ -18346,7 +18343,7 @@
         <v>10320</v>
       </c>
       <c r="E247" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F247" s="186">
         <v>8</v>
@@ -18508,7 +18505,7 @@
       <c r="C249" s="172"/>
       <c r="D249" s="248"/>
       <c r="E249" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F249" s="199"/>
       <c r="G249" s="200"/>
@@ -18642,7 +18639,7 @@
         <v>50</v>
       </c>
       <c r="B252" s="172" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C252" s="252" t="s">
         <v>33</v>
@@ -18651,7 +18648,7 @@
         <v>10320</v>
       </c>
       <c r="E252" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F252" s="186">
         <v>8</v>
@@ -18805,7 +18802,7 @@
       <c r="C254" s="250"/>
       <c r="D254" s="248"/>
       <c r="E254" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F254" s="199"/>
       <c r="G254" s="200"/>
@@ -18941,7 +18938,7 @@
         <v>51</v>
       </c>
       <c r="B257" s="159" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C257" s="159" t="s">
         <v>28</v>
@@ -18950,7 +18947,7 @@
         <v>10320</v>
       </c>
       <c r="E257" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F257" s="186">
         <v>8</v>
@@ -19112,7 +19109,7 @@
       <c r="C259" s="172"/>
       <c r="D259" s="248"/>
       <c r="E259" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F259" s="199"/>
       <c r="G259" s="200"/>
@@ -19246,7 +19243,7 @@
         <v>52</v>
       </c>
       <c r="B262" s="172" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C262" s="172" t="s">
         <v>28</v>
@@ -19255,7 +19252,7 @@
         <v>10320</v>
       </c>
       <c r="E262" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F262" s="186">
         <v>8</v>
@@ -19419,7 +19416,7 @@
       <c r="C264" s="172"/>
       <c r="D264" s="248"/>
       <c r="E264" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F264" s="199"/>
       <c r="G264" s="200"/>
@@ -19563,7 +19560,7 @@
         <v>53</v>
       </c>
       <c r="B267" s="159" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C267" s="159" t="s">
         <v>28</v>
@@ -19572,7 +19569,7 @@
         <v>10320</v>
       </c>
       <c r="E267" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F267" s="186">
         <v>8</v>
@@ -19718,7 +19715,7 @@
       <c r="C269" s="172"/>
       <c r="D269" s="248"/>
       <c r="E269" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F269" s="199"/>
       <c r="G269" s="200"/>
@@ -19854,7 +19851,7 @@
         <v>54</v>
       </c>
       <c r="B272" s="159" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C272" s="159" t="s">
         <v>28</v>
@@ -19863,7 +19860,7 @@
         <v>10320</v>
       </c>
       <c r="E272" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F272" s="186">
         <v>8</v>
@@ -20001,7 +19998,7 @@
       <c r="C274" s="172"/>
       <c r="D274" s="248"/>
       <c r="E274" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F274" s="199"/>
       <c r="G274" s="200"/>
@@ -20135,7 +20132,7 @@
         <v>55</v>
       </c>
       <c r="B277" s="172" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C277" s="258" t="s">
         <v>29</v>
@@ -20144,7 +20141,7 @@
         <v>10320</v>
       </c>
       <c r="E277" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F277" s="186">
         <v>8</v>
@@ -20258,7 +20255,7 @@
       <c r="C279" s="259"/>
       <c r="D279" s="248"/>
       <c r="E279" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F279" s="199"/>
       <c r="G279" s="200"/>
@@ -20392,7 +20389,7 @@
         <v>56</v>
       </c>
       <c r="B282" s="159" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C282" s="259" t="s">
         <v>29</v>
@@ -20401,7 +20398,7 @@
         <v>10320</v>
       </c>
       <c r="E282" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F282" s="186">
         <v>8</v>
@@ -20549,7 +20546,7 @@
       <c r="C284" s="259"/>
       <c r="D284" s="248"/>
       <c r="E284" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F284" s="199"/>
       <c r="G284" s="200"/>
@@ -20687,7 +20684,7 @@
         <v>57</v>
       </c>
       <c r="B287" s="172" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C287" s="252" t="s">
         <v>33</v>
@@ -20696,7 +20693,7 @@
         <v>10320</v>
       </c>
       <c r="E287" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F287" s="186">
         <v>8</v>
@@ -20806,7 +20803,7 @@
       <c r="C289" s="250"/>
       <c r="D289" s="248"/>
       <c r="E289" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F289" s="199"/>
       <c r="G289" s="200"/>
@@ -20940,7 +20937,7 @@
         <v>58</v>
       </c>
       <c r="B292" s="159" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C292" s="159" t="s">
         <v>28</v>
@@ -20949,7 +20946,7 @@
         <v>10320</v>
       </c>
       <c r="E292" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F292" s="186">
         <v>8</v>
@@ -21101,7 +21098,7 @@
       <c r="C294" s="172"/>
       <c r="D294" s="248"/>
       <c r="E294" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F294" s="199"/>
       <c r="G294" s="200"/>
@@ -21235,7 +21232,7 @@
         <v>59</v>
       </c>
       <c r="B297" s="159" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C297" s="159" t="s">
         <v>28</v>
@@ -21244,7 +21241,7 @@
         <v>10320</v>
       </c>
       <c r="E297" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F297" s="186">
         <v>8</v>
@@ -21350,7 +21347,7 @@
       <c r="C299" s="172"/>
       <c r="D299" s="248"/>
       <c r="E299" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F299" s="199"/>
       <c r="G299" s="200"/>
@@ -21484,7 +21481,7 @@
         <v>60</v>
       </c>
       <c r="B302" s="172" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C302" s="172" t="s">
         <v>28</v>
@@ -21493,7 +21490,7 @@
         <v>10320</v>
       </c>
       <c r="E302" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F302" s="186">
         <v>8</v>
@@ -21627,7 +21624,7 @@
       <c r="C304" s="172"/>
       <c r="D304" s="248"/>
       <c r="E304" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F304" s="199"/>
       <c r="G304" s="200"/>
@@ -21761,7 +21758,7 @@
         <v>61</v>
       </c>
       <c r="B307" s="159" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C307" s="159" t="s">
         <v>28</v>
@@ -21770,7 +21767,7 @@
         <v>10320</v>
       </c>
       <c r="E307" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F307" s="186">
         <v>8</v>
@@ -21940,7 +21937,7 @@
       <c r="C309" s="172"/>
       <c r="D309" s="248"/>
       <c r="E309" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F309" s="199"/>
       <c r="G309" s="200"/>
@@ -22084,7 +22081,7 @@
         <v>62</v>
       </c>
       <c r="B312" s="172" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C312" s="172" t="s">
         <v>28</v>
@@ -22093,7 +22090,7 @@
         <v>10320</v>
       </c>
       <c r="E312" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F312" s="186"/>
       <c r="G312" s="187">
@@ -22223,7 +22220,7 @@
       <c r="C314" s="172"/>
       <c r="D314" s="248"/>
       <c r="E314" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F314" s="199"/>
       <c r="G314" s="200"/>
@@ -22357,7 +22354,7 @@
         <v>63</v>
       </c>
       <c r="B317" s="159" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C317" s="159" t="s">
         <v>28</v>
@@ -22366,7 +22363,7 @@
         <v>10320</v>
       </c>
       <c r="E317" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F317" s="186">
         <v>8</v>
@@ -22502,7 +22499,7 @@
       <c r="C319" s="172"/>
       <c r="D319" s="248"/>
       <c r="E319" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F319" s="199"/>
       <c r="G319" s="200"/>
@@ -22636,7 +22633,7 @@
         <v>64</v>
       </c>
       <c r="B322" s="159" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C322" s="159" t="s">
         <v>28</v>
@@ -22645,7 +22642,7 @@
         <v>10320</v>
       </c>
       <c r="E322" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F322" s="186">
         <v>8</v>
@@ -22811,7 +22808,7 @@
       <c r="C324" s="172"/>
       <c r="D324" s="248"/>
       <c r="E324" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F324" s="199"/>
       <c r="G324" s="200"/>
@@ -22947,7 +22944,7 @@
         <v>65</v>
       </c>
       <c r="B327" s="159" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C327" s="159" t="s">
         <v>28</v>
@@ -22956,7 +22953,7 @@
         <v>10320</v>
       </c>
       <c r="E327" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F327" s="186">
         <v>8</v>
@@ -23094,7 +23091,7 @@
       <c r="C329" s="172"/>
       <c r="D329" s="248"/>
       <c r="E329" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F329" s="199"/>
       <c r="G329" s="200"/>
@@ -23228,7 +23225,7 @@
         <v>66</v>
       </c>
       <c r="B332" s="159" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C332" s="250" t="s">
         <v>33</v>
@@ -23237,7 +23234,7 @@
         <v>10320</v>
       </c>
       <c r="E332" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F332" s="186"/>
       <c r="G332" s="187">
@@ -23373,7 +23370,7 @@
       <c r="C334" s="252"/>
       <c r="D334" s="248"/>
       <c r="E334" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F334" s="199"/>
       <c r="G334" s="200"/>
@@ -23507,7 +23504,7 @@
         <v>67</v>
       </c>
       <c r="B337" s="159" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C337" s="159" t="s">
         <v>28</v>
@@ -23516,7 +23513,7 @@
         <v>10320</v>
       </c>
       <c r="E337" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F337" s="186">
         <v>8</v>
@@ -23624,7 +23621,7 @@
       <c r="C339" s="172"/>
       <c r="D339" s="248"/>
       <c r="E339" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F339" s="199"/>
       <c r="G339" s="200"/>
@@ -23758,7 +23755,7 @@
         <v>68</v>
       </c>
       <c r="B342" s="172" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C342" s="172" t="s">
         <v>28</v>
@@ -23767,7 +23764,7 @@
         <v>10320</v>
       </c>
       <c r="E342" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F342" s="186">
         <v>8</v>
@@ -23877,7 +23874,7 @@
       <c r="C344" s="172"/>
       <c r="D344" s="248"/>
       <c r="E344" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F344" s="199"/>
       <c r="G344" s="200"/>
@@ -24011,7 +24008,7 @@
         <v>69</v>
       </c>
       <c r="B347" s="159" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C347" s="159" t="s">
         <v>28</v>
@@ -24020,7 +24017,7 @@
         <v>10320</v>
       </c>
       <c r="E347" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F347" s="186"/>
       <c r="G347" s="187">
@@ -24152,7 +24149,7 @@
       <c r="C349" s="172"/>
       <c r="D349" s="248"/>
       <c r="E349" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F349" s="199"/>
       <c r="G349" s="200"/>
@@ -24286,7 +24283,7 @@
         <v>70</v>
       </c>
       <c r="B352" s="159" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C352" s="159" t="s">
         <v>28</v>
@@ -24295,7 +24292,7 @@
         <v>10320</v>
       </c>
       <c r="E352" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F352" s="186"/>
       <c r="G352" s="187">
@@ -24441,7 +24438,7 @@
       <c r="C354" s="172"/>
       <c r="D354" s="248"/>
       <c r="E354" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F354" s="199"/>
       <c r="G354" s="200"/>
@@ -24579,7 +24576,7 @@
         <v>71</v>
       </c>
       <c r="B357" s="159" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C357" s="250" t="s">
         <v>33</v>
@@ -24588,7 +24585,7 @@
         <v>10320</v>
       </c>
       <c r="E357" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F357" s="186"/>
       <c r="G357" s="187">
@@ -24700,7 +24697,7 @@
       <c r="C359" s="250"/>
       <c r="D359" s="248"/>
       <c r="E359" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F359" s="199"/>
       <c r="G359" s="200"/>
@@ -24834,7 +24831,7 @@
         <v>72</v>
       </c>
       <c r="B362" s="159" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C362" s="250" t="s">
         <v>33</v>
@@ -24843,7 +24840,7 @@
         <v>10320</v>
       </c>
       <c r="E362" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F362" s="186"/>
       <c r="G362" s="187">
@@ -24987,7 +24984,7 @@
       <c r="C364" s="250"/>
       <c r="D364" s="248"/>
       <c r="E364" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F364" s="199"/>
       <c r="G364" s="200"/>
@@ -25121,7 +25118,7 @@
         <v>73</v>
       </c>
       <c r="B367" s="172" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C367" s="252" t="s">
         <v>33</v>
@@ -25130,7 +25127,7 @@
         <v>10320</v>
       </c>
       <c r="E367" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F367" s="186"/>
       <c r="G367" s="187">
@@ -25236,7 +25233,7 @@
       <c r="C369" s="250"/>
       <c r="D369" s="248"/>
       <c r="E369" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F369" s="199"/>
       <c r="G369" s="200"/>
@@ -25372,7 +25369,7 @@
         <v>74</v>
       </c>
       <c r="B372" s="159" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C372" s="250" t="s">
         <v>33</v>
@@ -25381,7 +25378,7 @@
         <v>10320</v>
       </c>
       <c r="E372" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F372" s="186"/>
       <c r="G372" s="187">
@@ -25495,7 +25492,7 @@
       <c r="C374" s="250"/>
       <c r="D374" s="248"/>
       <c r="E374" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F374" s="199"/>
       <c r="G374" s="200"/>
@@ -25629,7 +25626,7 @@
         <v>75</v>
       </c>
       <c r="B377" s="159" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C377" s="159" t="s">
         <v>28</v>
@@ -25638,7 +25635,7 @@
         <v>10320</v>
       </c>
       <c r="E377" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F377" s="186"/>
       <c r="G377" s="244"/>
@@ -25748,7 +25745,7 @@
       <c r="C379" s="172"/>
       <c r="D379" s="248"/>
       <c r="E379" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F379" s="199"/>
       <c r="G379" s="245"/>
@@ -25882,7 +25879,7 @@
         <v>76</v>
       </c>
       <c r="B382" s="159" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C382" s="159" t="s">
         <v>28</v>
@@ -25891,7 +25888,7 @@
         <v>10320</v>
       </c>
       <c r="E382" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F382" s="186"/>
       <c r="G382" s="187">
@@ -26001,7 +25998,7 @@
       <c r="C384" s="172"/>
       <c r="D384" s="248"/>
       <c r="E384" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F384" s="199"/>
       <c r="G384" s="200"/>
@@ -26135,7 +26132,7 @@
         <v>77</v>
       </c>
       <c r="B387" s="159" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C387" s="159" t="s">
         <v>28</v>
@@ -26144,7 +26141,7 @@
         <v>10320</v>
       </c>
       <c r="E387" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F387" s="186"/>
       <c r="G387" s="244"/>
@@ -26264,7 +26261,7 @@
       <c r="C389" s="172"/>
       <c r="D389" s="248"/>
       <c r="E389" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F389" s="199"/>
       <c r="G389" s="245"/>
@@ -26400,7 +26397,7 @@
         <v>78</v>
       </c>
       <c r="B392" s="159" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C392" s="159" t="s">
         <v>28</v>
@@ -26409,7 +26406,7 @@
         <v>10320</v>
       </c>
       <c r="E392" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F392" s="186"/>
       <c r="G392" s="187">
@@ -26525,7 +26522,7 @@
       <c r="C394" s="172"/>
       <c r="D394" s="248"/>
       <c r="E394" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F394" s="199"/>
       <c r="G394" s="200"/>
@@ -26659,7 +26656,7 @@
         <v>79</v>
       </c>
       <c r="B397" s="159" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C397" s="159" t="s">
         <v>28</v>
@@ -26668,7 +26665,7 @@
         <v>10320</v>
       </c>
       <c r="E397" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F397" s="186"/>
       <c r="G397" s="187">
@@ -26766,7 +26763,7 @@
       <c r="C399" s="172"/>
       <c r="D399" s="248"/>
       <c r="E399" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F399" s="199"/>
       <c r="G399" s="200"/>
@@ -26900,7 +26897,7 @@
         <v>80</v>
       </c>
       <c r="B402" s="159" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C402" s="159" t="s">
         <v>28</v>
@@ -26909,7 +26906,7 @@
         <v>10320</v>
       </c>
       <c r="E402" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F402" s="186"/>
       <c r="G402" s="187">
@@ -27065,7 +27062,7 @@
       <c r="C404" s="172"/>
       <c r="D404" s="248"/>
       <c r="E404" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F404" s="199"/>
       <c r="G404" s="200"/>
@@ -27199,7 +27196,7 @@
         <v>81</v>
       </c>
       <c r="B407" s="159" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C407" s="159" t="s">
         <v>28</v>
@@ -27208,7 +27205,7 @@
         <v>10320</v>
       </c>
       <c r="E407" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F407" s="186"/>
       <c r="G407" s="187">
@@ -27340,7 +27337,7 @@
       <c r="C409" s="172"/>
       <c r="D409" s="248"/>
       <c r="E409" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F409" s="199"/>
       <c r="G409" s="200"/>
@@ -27476,7 +27473,7 @@
         <v>82</v>
       </c>
       <c r="B412" s="159" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C412" s="159" t="s">
         <v>28</v>
@@ -27485,7 +27482,7 @@
         <v>10320</v>
       </c>
       <c r="E412" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F412" s="186"/>
       <c r="G412" s="187">
@@ -27583,7 +27580,7 @@
       <c r="C414" s="172"/>
       <c r="D414" s="248"/>
       <c r="E414" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F414" s="199"/>
       <c r="G414" s="200"/>
@@ -27717,7 +27714,7 @@
         <v>83</v>
       </c>
       <c r="B417" s="159" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C417" s="159" t="s">
         <v>28</v>
@@ -27726,7 +27723,7 @@
         <v>10320</v>
       </c>
       <c r="E417" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F417" s="186"/>
       <c r="G417" s="187">
@@ -27824,7 +27821,7 @@
       <c r="C419" s="172"/>
       <c r="D419" s="248"/>
       <c r="E419" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F419" s="199"/>
       <c r="G419" s="200"/>
@@ -27958,7 +27955,7 @@
         <v>84</v>
       </c>
       <c r="B422" s="159" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C422" s="159" t="s">
         <v>28</v>
@@ -27967,7 +27964,7 @@
         <v>10320</v>
       </c>
       <c r="E422" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F422" s="186"/>
       <c r="G422" s="187">
@@ -28101,7 +28098,7 @@
       <c r="C424" s="172"/>
       <c r="D424" s="248"/>
       <c r="E424" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F424" s="199"/>
       <c r="G424" s="200"/>
@@ -28235,7 +28232,7 @@
         <v>85</v>
       </c>
       <c r="B427" s="159" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C427" s="250" t="s">
         <v>33</v>
@@ -28244,7 +28241,7 @@
         <v>10320</v>
       </c>
       <c r="E427" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F427" s="186"/>
       <c r="G427" s="187">
@@ -28342,7 +28339,7 @@
       <c r="C429" s="250"/>
       <c r="D429" s="248"/>
       <c r="E429" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F429" s="199"/>
       <c r="G429" s="200"/>
@@ -28476,7 +28473,7 @@
         <v>86</v>
       </c>
       <c r="B432" s="159" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C432" s="250" t="s">
         <v>33</v>
@@ -28485,7 +28482,7 @@
         <v>10320</v>
       </c>
       <c r="E432" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F432" s="186"/>
       <c r="G432" s="187">
@@ -28601,7 +28598,7 @@
       <c r="C434" s="250"/>
       <c r="D434" s="248"/>
       <c r="E434" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F434" s="199"/>
       <c r="G434" s="200"/>
@@ -28735,7 +28732,7 @@
         <v>87</v>
       </c>
       <c r="B437" s="159" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C437" s="159" t="s">
         <v>28</v>
@@ -28744,7 +28741,7 @@
         <v>10320</v>
       </c>
       <c r="E437" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F437" s="186"/>
       <c r="G437" s="187">
@@ -28838,7 +28835,7 @@
       <c r="C439" s="172"/>
       <c r="D439" s="248"/>
       <c r="E439" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F439" s="199"/>
       <c r="G439" s="200"/>
@@ -28972,7 +28969,7 @@
         <v>88</v>
       </c>
       <c r="B442" s="159" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C442" s="159" t="s">
         <v>28</v>
@@ -28981,7 +28978,7 @@
         <v>10320</v>
       </c>
       <c r="E442" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F442" s="186"/>
       <c r="G442" s="187">
@@ -29113,7 +29110,7 @@
       <c r="C444" s="172"/>
       <c r="D444" s="248"/>
       <c r="E444" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F444" s="199"/>
       <c r="G444" s="200"/>
@@ -29247,7 +29244,7 @@
         <v>89</v>
       </c>
       <c r="B447" s="159" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C447" s="250" t="s">
         <v>33</v>
@@ -29256,7 +29253,7 @@
         <v>10320</v>
       </c>
       <c r="E447" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F447" s="186"/>
       <c r="G447" s="187">
@@ -29396,7 +29393,7 @@
       <c r="C449" s="250"/>
       <c r="D449" s="248"/>
       <c r="E449" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F449" s="199"/>
       <c r="G449" s="200"/>
@@ -29530,7 +29527,7 @@
         <v>90</v>
       </c>
       <c r="B452" s="159" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C452" s="250" t="s">
         <v>33</v>
@@ -29539,7 +29536,7 @@
         <v>10320</v>
       </c>
       <c r="E452" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F452" s="186"/>
       <c r="G452" s="187">
@@ -29685,7 +29682,7 @@
       <c r="C454" s="250"/>
       <c r="D454" s="248"/>
       <c r="E454" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F454" s="199"/>
       <c r="G454" s="200"/>
@@ -29823,7 +29820,7 @@
         <v>91</v>
       </c>
       <c r="B457" s="159" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C457" s="159" t="s">
         <v>28</v>
@@ -29832,7 +29829,7 @@
         <v>10320</v>
       </c>
       <c r="E457" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F457" s="186"/>
       <c r="G457" s="187">
@@ -29930,7 +29927,7 @@
       <c r="C459" s="172"/>
       <c r="D459" s="248"/>
       <c r="E459" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F459" s="199"/>
       <c r="G459" s="200"/>
@@ -30064,7 +30061,7 @@
         <v>92</v>
       </c>
       <c r="B462" s="159" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C462" s="159" t="s">
         <v>28</v>
@@ -30073,7 +30070,7 @@
         <v>10320</v>
       </c>
       <c r="E462" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F462" s="186"/>
       <c r="G462" s="187">
@@ -30181,7 +30178,7 @@
       <c r="C464" s="172"/>
       <c r="D464" s="248"/>
       <c r="E464" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F464" s="199"/>
       <c r="G464" s="200"/>
@@ -30315,7 +30312,7 @@
         <v>93</v>
       </c>
       <c r="B467" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C467" s="159" t="s">
         <v>28</v>
@@ -30324,7 +30321,7 @@
         <v>10320</v>
       </c>
       <c r="E467" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F467" s="186"/>
       <c r="G467" s="187">
@@ -30418,7 +30415,7 @@
       <c r="C469" s="172"/>
       <c r="D469" s="248"/>
       <c r="E469" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F469" s="199"/>
       <c r="G469" s="200"/>
@@ -30552,7 +30549,7 @@
         <v>94</v>
       </c>
       <c r="B472" s="159" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C472" s="159" t="s">
         <v>28</v>
@@ -30561,7 +30558,7 @@
         <v>10320</v>
       </c>
       <c r="E472" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F472" s="186"/>
       <c r="G472" s="187">
@@ -30659,7 +30656,7 @@
       <c r="C474" s="172"/>
       <c r="D474" s="248"/>
       <c r="E474" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F474" s="199"/>
       <c r="G474" s="200"/>
@@ -30793,7 +30790,7 @@
         <v>95</v>
       </c>
       <c r="B477" s="159" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C477" s="250" t="s">
         <v>33</v>
@@ -30802,7 +30799,7 @@
         <v>10320</v>
       </c>
       <c r="E477" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F477" s="186"/>
       <c r="G477" s="187">
@@ -30948,7 +30945,7 @@
       <c r="C479" s="250"/>
       <c r="D479" s="248"/>
       <c r="E479" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F479" s="199"/>
       <c r="G479" s="200"/>
@@ -31086,7 +31083,7 @@
         <v>96</v>
       </c>
       <c r="B482" s="159" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C482" s="159" t="s">
         <v>28</v>
@@ -31095,7 +31092,7 @@
         <v>10320</v>
       </c>
       <c r="E482" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F482" s="186"/>
       <c r="G482" s="187">
@@ -31189,7 +31186,7 @@
       <c r="C484" s="172"/>
       <c r="D484" s="248"/>
       <c r="E484" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F484" s="199"/>
       <c r="G484" s="200"/>
@@ -31323,7 +31320,7 @@
         <v>97</v>
       </c>
       <c r="B487" s="159" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C487" s="159" t="s">
         <v>28</v>
@@ -31332,7 +31329,7 @@
         <v>10320</v>
       </c>
       <c r="E487" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F487" s="186"/>
       <c r="G487" s="187">
@@ -31426,7 +31423,7 @@
       <c r="C489" s="172"/>
       <c r="D489" s="248"/>
       <c r="E489" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F489" s="199"/>
       <c r="G489" s="200"/>
@@ -31560,7 +31557,7 @@
         <v>98</v>
       </c>
       <c r="B492" s="159" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C492" s="159" t="s">
         <v>28</v>
@@ -31569,7 +31566,7 @@
         <v>10320</v>
       </c>
       <c r="E492" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F492" s="186"/>
       <c r="G492" s="187">
@@ -31665,7 +31662,7 @@
       <c r="C494" s="172"/>
       <c r="D494" s="248"/>
       <c r="E494" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F494" s="199"/>
       <c r="G494" s="200"/>
@@ -31799,7 +31796,7 @@
         <v>99</v>
       </c>
       <c r="B497" s="159" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C497" s="159" t="s">
         <v>28</v>
@@ -31808,7 +31805,7 @@
         <v>10320</v>
       </c>
       <c r="E497" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F497" s="186"/>
       <c r="G497" s="187"/>
@@ -31900,7 +31897,7 @@
       <c r="C499" s="172"/>
       <c r="D499" s="248"/>
       <c r="E499" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F499" s="199"/>
       <c r="G499" s="200"/>
@@ -32034,7 +32031,7 @@
         <v>100</v>
       </c>
       <c r="B502" s="159" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C502" s="159" t="s">
         <v>28</v>
@@ -32043,7 +32040,7 @@
         <v>10320</v>
       </c>
       <c r="E502" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F502" s="186"/>
       <c r="G502" s="187"/>
@@ -32135,7 +32132,7 @@
       <c r="C504" s="172"/>
       <c r="D504" s="248"/>
       <c r="E504" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F504" s="199"/>
       <c r="G504" s="200"/>
@@ -32269,7 +32266,7 @@
         <v>101</v>
       </c>
       <c r="B507" s="159" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C507" s="159" t="s">
         <v>28</v>
@@ -32278,7 +32275,7 @@
         <v>10320</v>
       </c>
       <c r="E507" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F507" s="186"/>
       <c r="G507" s="187"/>
@@ -32378,7 +32375,7 @@
       <c r="C509" s="172"/>
       <c r="D509" s="248"/>
       <c r="E509" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F509" s="199"/>
       <c r="G509" s="200"/>
@@ -32512,7 +32509,7 @@
         <v>102</v>
       </c>
       <c r="B512" s="159" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C512" s="159" t="s">
         <v>28</v>
@@ -32521,7 +32518,7 @@
         <v>10320</v>
       </c>
       <c r="E512" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F512" s="186"/>
       <c r="G512" s="187"/>
@@ -32619,7 +32616,7 @@
       <c r="C514" s="172"/>
       <c r="D514" s="248"/>
       <c r="E514" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F514" s="199"/>
       <c r="G514" s="200"/>
@@ -32753,7 +32750,7 @@
         <v>103</v>
       </c>
       <c r="B517" s="159" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C517" s="159" t="s">
         <v>28</v>
@@ -32762,7 +32759,7 @@
         <v>10320</v>
       </c>
       <c r="E517" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F517" s="186"/>
       <c r="G517" s="187"/>
@@ -32862,7 +32859,7 @@
       <c r="C519" s="172"/>
       <c r="D519" s="248"/>
       <c r="E519" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F519" s="199"/>
       <c r="G519" s="200"/>
@@ -32996,7 +32993,7 @@
         <v>104</v>
       </c>
       <c r="B522" s="159" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C522" s="159" t="s">
         <v>28</v>
@@ -33005,7 +33002,7 @@
         <v>10320</v>
       </c>
       <c r="E522" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F522" s="186"/>
       <c r="G522" s="187"/>
@@ -33101,7 +33098,7 @@
       <c r="C524" s="172"/>
       <c r="D524" s="248"/>
       <c r="E524" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F524" s="199"/>
       <c r="G524" s="200"/>
@@ -33235,7 +33232,7 @@
         <v>105</v>
       </c>
       <c r="B527" s="159" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C527" s="159" t="s">
         <v>28</v>
@@ -33244,7 +33241,7 @@
         <v>10320</v>
       </c>
       <c r="E527" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F527" s="186"/>
       <c r="G527" s="187"/>
@@ -33340,7 +33337,7 @@
       <c r="C529" s="172"/>
       <c r="D529" s="248"/>
       <c r="E529" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F529" s="199"/>
       <c r="G529" s="200"/>
@@ -33474,7 +33471,7 @@
         <v>106</v>
       </c>
       <c r="B532" s="159" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C532" s="159" t="s">
         <v>28</v>
@@ -33483,7 +33480,7 @@
         <v>10320</v>
       </c>
       <c r="E532" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F532" s="186"/>
       <c r="G532" s="187"/>
@@ -33577,7 +33574,7 @@
       <c r="C534" s="172"/>
       <c r="D534" s="248"/>
       <c r="E534" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F534" s="199"/>
       <c r="G534" s="200"/>
@@ -33711,7 +33708,7 @@
         <v>107</v>
       </c>
       <c r="B537" s="159" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C537" s="159" t="s">
         <v>28</v>
@@ -33720,7 +33717,7 @@
         <v>10320</v>
       </c>
       <c r="E537" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F537" s="186"/>
       <c r="G537" s="187"/>
@@ -33812,7 +33809,7 @@
       <c r="C539" s="172"/>
       <c r="D539" s="248"/>
       <c r="E539" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F539" s="199"/>
       <c r="G539" s="200"/>
@@ -33946,7 +33943,7 @@
         <v>108</v>
       </c>
       <c r="B542" s="159" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C542" s="159" t="s">
         <v>28</v>
@@ -33955,7 +33952,7 @@
         <v>10320</v>
       </c>
       <c r="E542" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F542" s="186"/>
       <c r="G542" s="187"/>
@@ -34049,7 +34046,7 @@
       <c r="C544" s="172"/>
       <c r="D544" s="248"/>
       <c r="E544" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F544" s="199"/>
       <c r="G544" s="200"/>
@@ -34183,7 +34180,7 @@
         <v>109</v>
       </c>
       <c r="B547" s="159" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C547" s="159" t="s">
         <v>28</v>
@@ -34192,7 +34189,7 @@
         <v>10320</v>
       </c>
       <c r="E547" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F547" s="186"/>
       <c r="G547" s="187"/>
@@ -34284,7 +34281,7 @@
       <c r="C549" s="172"/>
       <c r="D549" s="248"/>
       <c r="E549" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F549" s="199"/>
       <c r="G549" s="200"/>
@@ -34423,7 +34420,7 @@
         <v>10320</v>
       </c>
       <c r="E552" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F552" s="271"/>
       <c r="G552" s="272"/>
@@ -34513,7 +34510,7 @@
       <c r="C554" s="172"/>
       <c r="D554" s="248"/>
       <c r="E554" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F554" s="275"/>
       <c r="G554" s="276"/>
@@ -34652,7 +34649,7 @@
         <v>10320</v>
       </c>
       <c r="E557" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F557" s="280"/>
       <c r="G557" s="187"/>
@@ -34742,7 +34739,7 @@
       <c r="C559" s="172"/>
       <c r="D559" s="248"/>
       <c r="E559" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F559" s="275"/>
       <c r="G559" s="276"/>
@@ -34881,7 +34878,7 @@
         <v>10320</v>
       </c>
       <c r="E562" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F562" s="271"/>
       <c r="G562" s="272"/>
@@ -34971,7 +34968,7 @@
       <c r="C564" s="172"/>
       <c r="D564" s="248"/>
       <c r="E564" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F564" s="275"/>
       <c r="G564" s="276"/>
@@ -35110,7 +35107,7 @@
         <v>10320</v>
       </c>
       <c r="E567" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F567" s="280"/>
       <c r="G567" s="187"/>
@@ -35200,7 +35197,7 @@
       <c r="C569" s="172"/>
       <c r="D569" s="248"/>
       <c r="E569" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F569" s="275"/>
       <c r="G569" s="276"/>
@@ -35339,7 +35336,7 @@
         <v>10320</v>
       </c>
       <c r="E572" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F572" s="271"/>
       <c r="G572" s="272"/>
@@ -35429,7 +35426,7 @@
       <c r="C574" s="172"/>
       <c r="D574" s="248"/>
       <c r="E574" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F574" s="275"/>
       <c r="G574" s="276"/>
@@ -35568,7 +35565,7 @@
         <v>10320</v>
       </c>
       <c r="E577" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F577" s="280"/>
       <c r="G577" s="187"/>
@@ -35658,7 +35655,7 @@
       <c r="C579" s="172"/>
       <c r="D579" s="248"/>
       <c r="E579" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F579" s="275"/>
       <c r="G579" s="276"/>
@@ -35797,7 +35794,7 @@
         <v>10320</v>
       </c>
       <c r="E582" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F582" s="271"/>
       <c r="G582" s="272"/>
@@ -35887,7 +35884,7 @@
       <c r="C584" s="159"/>
       <c r="D584" s="248"/>
       <c r="E584" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F584" s="275"/>
       <c r="G584" s="276"/>
@@ -36026,7 +36023,7 @@
         <v>10320</v>
       </c>
       <c r="E587" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F587" s="280"/>
       <c r="G587" s="187"/>
@@ -36116,7 +36113,7 @@
       <c r="C589" s="159"/>
       <c r="D589" s="248"/>
       <c r="E589" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F589" s="275"/>
       <c r="G589" s="276"/>
@@ -36255,7 +36252,7 @@
         <v>10320</v>
       </c>
       <c r="E592" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F592" s="271"/>
       <c r="G592" s="272"/>
@@ -36345,7 +36342,7 @@
       <c r="C594" s="159"/>
       <c r="D594" s="248"/>
       <c r="E594" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F594" s="275"/>
       <c r="G594" s="276"/>
@@ -36484,7 +36481,7 @@
         <v>10320</v>
       </c>
       <c r="E597" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F597" s="280"/>
       <c r="G597" s="187"/>
@@ -36574,7 +36571,7 @@
       <c r="C599" s="159"/>
       <c r="D599" s="248"/>
       <c r="E599" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F599" s="275"/>
       <c r="G599" s="276"/>
@@ -36713,7 +36710,7 @@
         <v>10320</v>
       </c>
       <c r="E602" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F602" s="271"/>
       <c r="G602" s="272"/>
@@ -36803,7 +36800,7 @@
       <c r="C604" s="172"/>
       <c r="D604" s="248"/>
       <c r="E604" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F604" s="275"/>
       <c r="G604" s="276"/>
@@ -36942,7 +36939,7 @@
         <v>10320</v>
       </c>
       <c r="E607" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F607" s="280"/>
       <c r="G607" s="187"/>
@@ -37032,7 +37029,7 @@
       <c r="C609" s="159"/>
       <c r="D609" s="248"/>
       <c r="E609" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F609" s="275"/>
       <c r="G609" s="276"/>
@@ -37171,7 +37168,7 @@
         <v>10320</v>
       </c>
       <c r="E612" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F612" s="271"/>
       <c r="G612" s="272"/>
@@ -37261,7 +37258,7 @@
       <c r="C614" s="159"/>
       <c r="D614" s="248"/>
       <c r="E614" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F614" s="275"/>
       <c r="G614" s="276"/>
@@ -37400,7 +37397,7 @@
         <v>10320</v>
       </c>
       <c r="E617" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F617" s="271"/>
       <c r="G617" s="272"/>
@@ -37490,7 +37487,7 @@
       <c r="C619" s="172"/>
       <c r="D619" s="248"/>
       <c r="E619" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F619" s="275"/>
       <c r="G619" s="276"/>
@@ -37629,7 +37626,7 @@
         <v>10320</v>
       </c>
       <c r="E622" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F622" s="271"/>
       <c r="G622" s="272"/>
@@ -37719,7 +37716,7 @@
       <c r="C624" s="159"/>
       <c r="D624" s="248"/>
       <c r="E624" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F624" s="275"/>
       <c r="G624" s="276"/>
@@ -37858,7 +37855,7 @@
         <v>10320</v>
       </c>
       <c r="E627" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F627" s="280"/>
       <c r="G627" s="187"/>
@@ -37948,7 +37945,7 @@
       <c r="C629" s="172"/>
       <c r="D629" s="248"/>
       <c r="E629" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F629" s="275"/>
       <c r="G629" s="276"/>
@@ -38087,7 +38084,7 @@
         <v>10320</v>
       </c>
       <c r="E632" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F632" s="271"/>
       <c r="G632" s="272"/>
@@ -38177,7 +38174,7 @@
       <c r="C634" s="159"/>
       <c r="D634" s="248"/>
       <c r="E634" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F634" s="275"/>
       <c r="G634" s="276"/>
@@ -38316,7 +38313,7 @@
         <v>10320</v>
       </c>
       <c r="E637" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F637" s="280"/>
       <c r="G637" s="187"/>
@@ -38406,7 +38403,7 @@
       <c r="C639" s="159"/>
       <c r="D639" s="248"/>
       <c r="E639" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F639" s="275"/>
       <c r="G639" s="276"/>
@@ -38545,7 +38542,7 @@
         <v>10320</v>
       </c>
       <c r="E642" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F642" s="271"/>
       <c r="G642" s="272"/>
@@ -38635,7 +38632,7 @@
       <c r="C644" s="159"/>
       <c r="D644" s="248"/>
       <c r="E644" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F644" s="275"/>
       <c r="G644" s="276"/>
@@ -38774,7 +38771,7 @@
         <v>10320</v>
       </c>
       <c r="E647" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F647" s="280"/>
       <c r="G647" s="187"/>
@@ -38864,7 +38861,7 @@
       <c r="C649" s="172"/>
       <c r="D649" s="248"/>
       <c r="E649" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F649" s="275"/>
       <c r="G649" s="276"/>
@@ -39003,7 +39000,7 @@
         <v>10320</v>
       </c>
       <c r="E652" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F652" s="271"/>
       <c r="G652" s="272"/>
@@ -39093,7 +39090,7 @@
       <c r="C654" s="172"/>
       <c r="D654" s="248"/>
       <c r="E654" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F654" s="275"/>
       <c r="G654" s="276"/>
@@ -39232,7 +39229,7 @@
         <v>10320</v>
       </c>
       <c r="E657" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F657" s="280"/>
       <c r="G657" s="187"/>
@@ -39322,7 +39319,7 @@
       <c r="C659" s="172"/>
       <c r="D659" s="248"/>
       <c r="E659" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F659" s="275"/>
       <c r="G659" s="276"/>
@@ -39461,7 +39458,7 @@
         <v>10320</v>
       </c>
       <c r="E662" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F662" s="271"/>
       <c r="G662" s="272"/>
@@ -39551,7 +39548,7 @@
       <c r="C664" s="172"/>
       <c r="D664" s="248"/>
       <c r="E664" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F664" s="275"/>
       <c r="G664" s="276"/>
@@ -39690,7 +39687,7 @@
         <v>10320</v>
       </c>
       <c r="E667" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F667" s="280"/>
       <c r="G667" s="187"/>
@@ -39780,7 +39777,7 @@
       <c r="C669" s="172"/>
       <c r="D669" s="248"/>
       <c r="E669" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F669" s="275"/>
       <c r="G669" s="276"/>
@@ -39919,7 +39916,7 @@
         <v>10320</v>
       </c>
       <c r="E672" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F672" s="271"/>
       <c r="G672" s="272"/>
@@ -40009,7 +40006,7 @@
       <c r="C674" s="172"/>
       <c r="D674" s="248"/>
       <c r="E674" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F674" s="275"/>
       <c r="G674" s="276"/>
@@ -40148,7 +40145,7 @@
         <v>10320</v>
       </c>
       <c r="E677" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F677" s="280"/>
       <c r="G677" s="187"/>
@@ -40238,7 +40235,7 @@
       <c r="C679" s="172"/>
       <c r="D679" s="248"/>
       <c r="E679" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F679" s="275"/>
       <c r="G679" s="276"/>
@@ -40377,7 +40374,7 @@
         <v>10320</v>
       </c>
       <c r="E682" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F682" s="271"/>
       <c r="G682" s="272"/>
@@ -40467,7 +40464,7 @@
       <c r="C684" s="172"/>
       <c r="D684" s="248"/>
       <c r="E684" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F684" s="275"/>
       <c r="G684" s="276"/>
@@ -40606,7 +40603,7 @@
         <v>10320</v>
       </c>
       <c r="E687" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F687" s="280"/>
       <c r="G687" s="187"/>
@@ -40696,7 +40693,7 @@
       <c r="C689" s="172"/>
       <c r="D689" s="248"/>
       <c r="E689" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F689" s="275"/>
       <c r="G689" s="276"/>
@@ -40835,7 +40832,7 @@
         <v>10320</v>
       </c>
       <c r="E692" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F692" s="271"/>
       <c r="G692" s="272"/>
@@ -40925,7 +40922,7 @@
       <c r="C694" s="172"/>
       <c r="D694" s="248"/>
       <c r="E694" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F694" s="275"/>
       <c r="G694" s="276"/>
@@ -41064,7 +41061,7 @@
         <v>10320</v>
       </c>
       <c r="E697" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F697" s="280"/>
       <c r="G697" s="187"/>
@@ -41154,7 +41151,7 @@
       <c r="C699" s="172"/>
       <c r="D699" s="248"/>
       <c r="E699" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F699" s="275"/>
       <c r="G699" s="276"/>
@@ -41293,7 +41290,7 @@
         <v>10320</v>
       </c>
       <c r="E702" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F702" s="271"/>
       <c r="G702" s="272"/>
@@ -41383,7 +41380,7 @@
       <c r="C704" s="172"/>
       <c r="D704" s="248"/>
       <c r="E704" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F704" s="275"/>
       <c r="G704" s="276"/>
@@ -41522,7 +41519,7 @@
         <v>10320</v>
       </c>
       <c r="E707" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F707" s="280"/>
       <c r="G707" s="187"/>
@@ -41612,7 +41609,7 @@
       <c r="C709" s="172"/>
       <c r="D709" s="248"/>
       <c r="E709" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F709" s="275"/>
       <c r="G709" s="276"/>
@@ -41751,7 +41748,7 @@
         <v>10320</v>
       </c>
       <c r="E712" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F712" s="271"/>
       <c r="G712" s="272"/>
@@ -41841,7 +41838,7 @@
       <c r="C714" s="172"/>
       <c r="D714" s="248"/>
       <c r="E714" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F714" s="275"/>
       <c r="G714" s="276"/>
@@ -41980,7 +41977,7 @@
         <v>10320</v>
       </c>
       <c r="E717" s="234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F717" s="280"/>
       <c r="G717" s="187"/>
@@ -42070,7 +42067,7 @@
       <c r="C719" s="172"/>
       <c r="D719" s="248"/>
       <c r="E719" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F719" s="275"/>
       <c r="G719" s="276"/>
@@ -42209,7 +42206,7 @@
         <v>10320</v>
       </c>
       <c r="E722" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F722" s="271"/>
       <c r="G722" s="272"/>
@@ -42299,7 +42296,7 @@
       <c r="C724" s="172"/>
       <c r="D724" s="248"/>
       <c r="E724" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F724" s="275"/>
       <c r="G724" s="276"/>
@@ -42438,7 +42435,7 @@
         <v>10320</v>
       </c>
       <c r="E727" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F727" s="271"/>
       <c r="G727" s="272"/>
@@ -42528,7 +42525,7 @@
       <c r="C729" s="172"/>
       <c r="D729" s="248"/>
       <c r="E729" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F729" s="275"/>
       <c r="G729" s="276"/>
@@ -42667,7 +42664,7 @@
         <v>10320</v>
       </c>
       <c r="E732" s="287" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F732" s="288"/>
       <c r="G732" s="187"/>
@@ -42757,7 +42754,7 @@
       <c r="C734" s="172"/>
       <c r="D734" s="248"/>
       <c r="E734" s="290" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F734" s="291"/>
       <c r="G734" s="276"/>
@@ -42896,7 +42893,7 @@
         <v>10320</v>
       </c>
       <c r="E737" s="295" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F737" s="288"/>
       <c r="G737" s="187"/>
@@ -42986,7 +42983,7 @@
       <c r="C739" s="172"/>
       <c r="D739" s="248"/>
       <c r="E739" s="290" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F739" s="291"/>
       <c r="G739" s="276"/>
@@ -43125,7 +43122,7 @@
         <v>10320</v>
       </c>
       <c r="E742" s="295" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F742" s="288"/>
       <c r="G742" s="187"/>
@@ -43215,7 +43212,7 @@
       <c r="C744" s="172"/>
       <c r="D744" s="248"/>
       <c r="E744" s="290" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F744" s="291"/>
       <c r="G744" s="276"/>
@@ -43354,7 +43351,7 @@
         <v>10320</v>
       </c>
       <c r="E747" s="295" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F747" s="288"/>
       <c r="G747" s="187"/>
@@ -43444,7 +43441,7 @@
       <c r="C749" s="172"/>
       <c r="D749" s="248"/>
       <c r="E749" s="290" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F749" s="291"/>
       <c r="G749" s="276"/>
@@ -43583,7 +43580,7 @@
         <v>10320</v>
       </c>
       <c r="E752" s="295" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F752" s="288"/>
       <c r="G752" s="187"/>
@@ -43673,7 +43670,7 @@
       <c r="C754" s="172"/>
       <c r="D754" s="248"/>
       <c r="E754" s="290" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F754" s="291"/>
       <c r="G754" s="276"/>
@@ -43812,7 +43809,7 @@
         <v>10320</v>
       </c>
       <c r="E757" s="295" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F757" s="288"/>
       <c r="G757" s="187"/>
@@ -43902,7 +43899,7 @@
       <c r="C759" s="172"/>
       <c r="D759" s="248"/>
       <c r="E759" s="290" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F759" s="291"/>
       <c r="G759" s="276"/>
@@ -44041,7 +44038,7 @@
         <v>10320</v>
       </c>
       <c r="E762" s="295" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F762" s="288"/>
       <c r="G762" s="187"/>
@@ -44131,7 +44128,7 @@
       <c r="C764" s="172"/>
       <c r="D764" s="248"/>
       <c r="E764" s="290" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F764" s="291"/>
       <c r="G764" s="276"/>
@@ -44270,7 +44267,7 @@
         <v>10320</v>
       </c>
       <c r="E767" s="295" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F767" s="288"/>
       <c r="G767" s="187"/>
@@ -44360,7 +44357,7 @@
       <c r="C769" s="172"/>
       <c r="D769" s="248"/>
       <c r="E769" s="290" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F769" s="291"/>
       <c r="G769" s="276"/>
@@ -44499,7 +44496,7 @@
         <v>10320</v>
       </c>
       <c r="E772" s="295" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F772" s="288"/>
       <c r="G772" s="187"/>
@@ -44589,7 +44586,7 @@
       <c r="C774" s="172"/>
       <c r="D774" s="248"/>
       <c r="E774" s="290" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F774" s="291"/>
       <c r="G774" s="276"/>
@@ -44728,7 +44725,7 @@
         <v>10320</v>
       </c>
       <c r="E777" s="295" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F777" s="288"/>
       <c r="G777" s="187"/>
@@ -44818,7 +44815,7 @@
       <c r="C779" s="172"/>
       <c r="D779" s="248"/>
       <c r="E779" s="290" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F779" s="291"/>
       <c r="G779" s="276"/>
@@ -44957,7 +44954,7 @@
         <v>10320</v>
       </c>
       <c r="E782" s="295" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F782" s="288"/>
       <c r="G782" s="187"/>
@@ -45047,7 +45044,7 @@
       <c r="C784" s="172"/>
       <c r="D784" s="248"/>
       <c r="E784" s="290" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F784" s="291"/>
       <c r="G784" s="276"/>
@@ -45186,7 +45183,7 @@
         <v>10320</v>
       </c>
       <c r="E787" s="295" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F787" s="288"/>
       <c r="G787" s="187"/>
@@ -45276,7 +45273,7 @@
       <c r="C789" s="172"/>
       <c r="D789" s="248"/>
       <c r="E789" s="290" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F789" s="291"/>
       <c r="G789" s="276"/>
@@ -45415,7 +45412,7 @@
         <v>10320</v>
       </c>
       <c r="E792" s="295" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F792" s="288"/>
       <c r="G792" s="187"/>
@@ -45505,7 +45502,7 @@
       <c r="C794" s="172"/>
       <c r="D794" s="248"/>
       <c r="E794" s="290" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F794" s="291"/>
       <c r="G794" s="276"/>
@@ -45644,7 +45641,7 @@
         <v>10320</v>
       </c>
       <c r="E797" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F797" s="288"/>
       <c r="G797" s="187"/>
@@ -45734,7 +45731,7 @@
       <c r="C799" s="172"/>
       <c r="D799" s="248"/>
       <c r="E799" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F799" s="291"/>
       <c r="G799" s="276"/>
@@ -45873,7 +45870,7 @@
         <v>10320</v>
       </c>
       <c r="E802" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F802" s="288"/>
       <c r="G802" s="187"/>
@@ -45963,7 +45960,7 @@
       <c r="C804" s="172"/>
       <c r="D804" s="248"/>
       <c r="E804" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F804" s="291"/>
       <c r="G804" s="276"/>
@@ -46102,7 +46099,7 @@
         <v>10320</v>
       </c>
       <c r="E807" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F807" s="288"/>
       <c r="G807" s="187"/>
@@ -46192,7 +46189,7 @@
       <c r="C809" s="172"/>
       <c r="D809" s="248"/>
       <c r="E809" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F809" s="291"/>
       <c r="G809" s="276"/>
@@ -46331,7 +46328,7 @@
         <v>10320</v>
       </c>
       <c r="E812" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F812" s="288"/>
       <c r="G812" s="187"/>
@@ -46421,7 +46418,7 @@
       <c r="C814" s="172"/>
       <c r="D814" s="248"/>
       <c r="E814" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F814" s="291"/>
       <c r="G814" s="276"/>
@@ -46560,7 +46557,7 @@
         <v>10320</v>
       </c>
       <c r="E817" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F817" s="288"/>
       <c r="G817" s="187"/>
@@ -46650,7 +46647,7 @@
       <c r="C819" s="172"/>
       <c r="D819" s="248"/>
       <c r="E819" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F819" s="291"/>
       <c r="G819" s="276"/>
@@ -46789,7 +46786,7 @@
         <v>10320</v>
       </c>
       <c r="E822" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F822" s="288"/>
       <c r="G822" s="187"/>
@@ -46879,7 +46876,7 @@
       <c r="C824" s="172"/>
       <c r="D824" s="248"/>
       <c r="E824" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F824" s="291"/>
       <c r="G824" s="276"/>
@@ -47018,7 +47015,7 @@
         <v>10320</v>
       </c>
       <c r="E827" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F827" s="288"/>
       <c r="G827" s="187"/>
@@ -47108,7 +47105,7 @@
       <c r="C829" s="172"/>
       <c r="D829" s="248"/>
       <c r="E829" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F829" s="291"/>
       <c r="G829" s="276"/>
@@ -47247,7 +47244,7 @@
         <v>10320</v>
       </c>
       <c r="E832" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F832" s="288"/>
       <c r="G832" s="187"/>
@@ -47337,7 +47334,7 @@
       <c r="C834" s="172"/>
       <c r="D834" s="248"/>
       <c r="E834" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F834" s="291"/>
       <c r="G834" s="276"/>
@@ -47476,7 +47473,7 @@
         <v>10320</v>
       </c>
       <c r="E837" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F837" s="288"/>
       <c r="G837" s="187"/>
@@ -47566,7 +47563,7 @@
       <c r="C839" s="172"/>
       <c r="D839" s="248"/>
       <c r="E839" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F839" s="291"/>
       <c r="G839" s="276"/>
@@ -47705,7 +47702,7 @@
         <v>10320</v>
       </c>
       <c r="E842" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F842" s="288"/>
       <c r="G842" s="187"/>
@@ -47795,7 +47792,7 @@
       <c r="C844" s="172"/>
       <c r="D844" s="248"/>
       <c r="E844" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F844" s="291"/>
       <c r="G844" s="276"/>
@@ -47934,7 +47931,7 @@
         <v>10320</v>
       </c>
       <c r="E847" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F847" s="288"/>
       <c r="G847" s="187"/>
@@ -48024,7 +48021,7 @@
       <c r="C849" s="172"/>
       <c r="D849" s="248"/>
       <c r="E849" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F849" s="291"/>
       <c r="G849" s="276"/>
@@ -48163,7 +48160,7 @@
         <v>10320</v>
       </c>
       <c r="E852" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F852" s="288"/>
       <c r="G852" s="187"/>
@@ -48253,7 +48250,7 @@
       <c r="C854" s="172"/>
       <c r="D854" s="248"/>
       <c r="E854" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F854" s="291"/>
       <c r="G854" s="276"/>
@@ -48392,7 +48389,7 @@
         <v>10320</v>
       </c>
       <c r="E857" s="185" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F857" s="288"/>
       <c r="G857" s="187"/>
@@ -48482,7 +48479,7 @@
       <c r="C859" s="172"/>
       <c r="D859" s="248"/>
       <c r="E859" s="198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F859" s="291"/>
       <c r="G859" s="276"/>
@@ -50311,7 +50308,7 @@
     <col min="16" max="16" width="11.625" style="58" customWidth="1"/>
     <col min="17" max="18" width="9.875" style="58" customWidth="1"/>
     <col min="19" max="19" width="11.75" style="58" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="8.875" style="58" hidden="1" customWidth="1"/>
+    <col min="20" max="20" style="58" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13.375" style="58" customWidth="1"/>
     <col min="22" max="23" width="12.375" style="59" customWidth="1"/>
     <col min="24" max="24" width="10.875" style="59" customWidth="1"/>
@@ -52483,38 +52480,36 @@
       <c r="S3" s="82" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="82" t="s">
+      <c r="T3" s="82"/>
+      <c r="U3" s="83" t="s">
         <v>44</v>
       </c>
-      <c r="U3" s="83" t="s">
+      <c r="V3" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="V3" s="84" t="s">
+      <c r="W3" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="W3" s="85" t="s">
+      <c r="X3" s="85" t="s">
         <v>47</v>
       </c>
-      <c r="X3" s="85" t="s">
+      <c r="Y3" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="Y3" s="85" t="s">
+      <c r="Z3" s="85" t="s">
         <v>49</v>
       </c>
-      <c r="Z3" s="85" t="s">
+      <c r="AA3" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="AA3" s="86" t="s">
+      <c r="AB3" s="85" t="s">
         <v>51</v>
       </c>
-      <c r="AB3" s="85" t="s">
+      <c r="AC3" s="85" t="s">
         <v>52</v>
       </c>
-      <c r="AC3" s="85" t="s">
+      <c r="AD3" s="87" t="s">
         <v>53</v>
-      </c>
-      <c r="AD3" s="87" t="s">
-        <v>54</v>
       </c>
       <c r="AE3" s="77"/>
       <c r="AF3" s="78"/>
@@ -52530,36 +52525,38 @@
       <c r="G4" s="80"/>
       <c r="H4" s="81"/>
       <c r="I4" s="80" t="s">
+        <v>54</v>
+      </c>
+      <c r="J4" s="81" t="s">
         <v>55</v>
       </c>
-      <c r="J4" s="81" t="s">
-        <v>56</v>
-      </c>
       <c r="K4" s="80" t="s">
+        <v>54</v>
+      </c>
+      <c r="L4" s="81" t="s">
         <v>55</v>
       </c>
-      <c r="L4" s="81" t="s">
-        <v>56</v>
-      </c>
       <c r="M4" s="80" t="s">
+        <v>54</v>
+      </c>
+      <c r="N4" s="81" t="s">
         <v>55</v>
       </c>
-      <c r="N4" s="81" t="s">
-        <v>56</v>
-      </c>
       <c r="O4" s="80" t="s">
+        <v>54</v>
+      </c>
+      <c r="P4" s="81" t="s">
         <v>55</v>
       </c>
-      <c r="P4" s="81" t="s">
-        <v>56</v>
-      </c>
       <c r="Q4" s="80" t="s">
+        <v>54</v>
+      </c>
+      <c r="R4" s="81" t="s">
         <v>55</v>
       </c>
-      <c r="R4" s="81" t="s">
-        <v>56</v>
-      </c>
-      <c r="S4" s="89"/>
+      <c r="S4" s="89" t="s">
+        <v>55</v>
+      </c>
       <c r="T4" s="89"/>
       <c r="U4" s="90"/>
       <c r="V4" s="84"/>
@@ -52583,7 +52580,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E5" s="93" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F5" s="94">
         <v>1</v>
@@ -52712,7 +52709,7 @@
         <v>섭주</v>
       </c>
       <c r="E6" s="93" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F6" s="94">
         <v>2</v>
@@ -52841,7 +52838,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E7" s="93" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F7" s="94">
         <v>3</v>
@@ -52970,7 +52967,7 @@
         <v>섭주</v>
       </c>
       <c r="E8" s="93" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F8" s="94">
         <v>4</v>
@@ -53096,7 +53093,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E9" s="93" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F9" s="94">
         <v>5</v>
@@ -53197,7 +53194,7 @@
         <v>섭주</v>
       </c>
       <c r="E10" s="93" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F10" s="94">
         <v>6</v>
@@ -53298,7 +53295,7 @@
         <v>섭주</v>
       </c>
       <c r="E11" s="93" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F11" s="94">
         <v>7</v>
@@ -53399,7 +53396,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E12" s="93" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F12" s="94">
         <v>8</v>
@@ -53500,7 +53497,7 @@
         <v>섭주</v>
       </c>
       <c r="E13" s="93" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F13" s="94">
         <v>9</v>
@@ -53601,7 +53598,7 @@
         <v>섭주</v>
       </c>
       <c r="E14" s="93" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F14" s="94">
         <v>10</v>
@@ -53702,7 +53699,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E15" s="93" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F15" s="94">
         <v>11</v>
@@ -53803,7 +53800,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E16" s="93" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F16" s="94">
         <v>12</v>
@@ -53904,7 +53901,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E17" s="93" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F17" s="94">
         <v>13</v>
@@ -54005,7 +54002,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E18" s="93" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F18" s="94">
         <v>14</v>
@@ -54106,7 +54103,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E19" s="93" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F19" s="94">
         <v>15</v>
@@ -54207,7 +54204,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E20" s="93" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F20" s="94">
         <v>16</v>
@@ -54308,7 +54305,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E21" s="93" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F21" s="94">
         <v>17</v>
@@ -54409,7 +54406,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E22" s="93" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F22" s="94">
         <v>18</v>
@@ -54510,7 +54507,7 @@
         <v>섭주</v>
       </c>
       <c r="E23" s="93" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F23" s="94">
         <v>19</v>
@@ -54611,7 +54608,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E24" s="93" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F24" s="94">
         <v>20</v>
@@ -54712,7 +54709,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E25" s="93" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F25" s="94">
         <v>21</v>
@@ -54813,7 +54810,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E26" s="93" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F26" s="94">
         <v>22</v>
@@ -54914,7 +54911,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E27" s="93" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F27" s="94">
         <v>23</v>
@@ -55015,7 +55012,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E28" s="93" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F28" s="94">
         <v>24</v>
@@ -55116,7 +55113,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E29" s="93" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F29" s="94">
         <v>25</v>
@@ -55217,7 +55214,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E30" s="93" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F30" s="94">
         <v>26</v>
@@ -55318,7 +55315,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E31" s="93" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F31" s="94">
         <v>27</v>
@@ -55419,7 +55416,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E32" s="93" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F32" s="94">
         <v>28</v>
@@ -55520,7 +55517,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E33" s="93" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F33" s="94">
         <v>29</v>
@@ -55621,7 +55618,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E34" s="93" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F34" s="94">
         <v>30</v>
@@ -55722,7 +55719,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E35" s="93" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F35" s="94">
         <v>31</v>
@@ -55823,7 +55820,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E36" s="93" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F36" s="94">
         <v>32</v>
@@ -55924,7 +55921,7 @@
         <v>케이위드</v>
       </c>
       <c r="E37" s="93" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F37" s="94">
         <v>33</v>
@@ -56025,7 +56022,7 @@
         <v>케이위드</v>
       </c>
       <c r="E38" s="93" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F38" s="94">
         <v>34</v>
@@ -56126,7 +56123,7 @@
         <v>케이위드</v>
       </c>
       <c r="E39" s="93" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F39" s="94">
         <v>35</v>
@@ -56227,7 +56224,7 @@
         <v>케이위드</v>
       </c>
       <c r="E40" s="93" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F40" s="94">
         <v>36</v>
@@ -56328,7 +56325,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E41" s="93" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F41" s="94">
         <v>37</v>
@@ -56429,7 +56426,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E42" s="93" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F42" s="94">
         <v>38</v>
@@ -56530,7 +56527,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E43" s="93" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F43" s="94">
         <v>39</v>
@@ -56631,7 +56628,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E44" s="93" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F44" s="94">
         <v>40</v>
@@ -56732,7 +56729,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E45" s="93" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F45" s="94">
         <v>41</v>
@@ -56833,7 +56830,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E46" s="93" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F46" s="94">
         <v>42</v>
@@ -56934,7 +56931,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E47" s="93" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F47" s="94">
         <v>43</v>
@@ -57035,7 +57032,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E48" s="93" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F48" s="94">
         <v>44</v>
@@ -57136,7 +57133,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E49" s="93" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F49" s="94">
         <v>45</v>
@@ -57237,7 +57234,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E50" s="93" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F50" s="94">
         <v>46</v>
@@ -57335,7 +57332,7 @@
         <v>케이위드</v>
       </c>
       <c r="E51" s="93" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F51" s="94">
         <v>47</v>
@@ -57433,7 +57430,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E52" s="93" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F52" s="94">
         <v>48</v>
@@ -57531,7 +57528,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E53" s="93" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F53" s="94">
         <v>49</v>
@@ -57629,7 +57626,7 @@
         <v>케이위드</v>
       </c>
       <c r="E54" s="93" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F54" s="94">
         <v>50</v>
@@ -57727,7 +57724,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E55" s="93" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F55" s="94">
         <v>51</v>
@@ -57825,7 +57822,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E56" s="93" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F56" s="94">
         <v>52</v>
@@ -57923,7 +57920,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E57" s="93" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F57" s="94">
         <v>53</v>
@@ -58021,7 +58018,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E58" s="93" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F58" s="94">
         <v>54</v>
@@ -58122,7 +58119,7 @@
         <v>로얄</v>
       </c>
       <c r="E59" s="93" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F59" s="94">
         <v>55</v>
@@ -58220,7 +58217,7 @@
         <v>로얄</v>
       </c>
       <c r="E60" s="93" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F60" s="94">
         <v>56</v>
@@ -58321,7 +58318,7 @@
         <v>케이위드</v>
       </c>
       <c r="E61" s="93" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F61" s="94">
         <v>57</v>
@@ -58422,7 +58419,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E62" s="93" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F62" s="94">
         <v>58</v>
@@ -58520,7 +58517,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E63" s="93" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F63" s="94">
         <v>59</v>
@@ -58618,7 +58615,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E64" s="93" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F64" s="94">
         <v>60</v>
@@ -58716,7 +58713,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E65" s="93" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F65" s="94">
         <v>61</v>
@@ -58814,7 +58811,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E66" s="93" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F66" s="94">
         <v>62</v>
@@ -58912,7 +58909,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E67" s="93" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F67" s="94">
         <v>63</v>
@@ -59010,7 +59007,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E68" s="93" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F68" s="94">
         <v>64</v>
@@ -59108,7 +59105,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E69" s="93" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F69" s="94">
         <v>65</v>
@@ -59206,7 +59203,7 @@
         <v>케이위드</v>
       </c>
       <c r="E70" s="93" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F70" s="94">
         <v>66</v>
@@ -59304,7 +59301,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E71" s="93" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F71" s="94">
         <v>67</v>
@@ -59402,7 +59399,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E72" s="93" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F72" s="94">
         <v>68</v>
@@ -59500,7 +59497,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E73" s="93" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F73" s="94">
         <v>69</v>
@@ -59601,7 +59598,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E74" s="93" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F74" s="94">
         <v>70</v>
@@ -59702,7 +59699,7 @@
         <v>케이위드</v>
       </c>
       <c r="E75" s="93" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F75" s="94">
         <v>71</v>
@@ -59800,7 +59797,7 @@
         <v>케이위드</v>
       </c>
       <c r="E76" s="93" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F76" s="94">
         <v>72</v>
@@ -59898,7 +59895,7 @@
         <v>케이위드</v>
       </c>
       <c r="E77" s="93" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F77" s="94">
         <v>73</v>
@@ -59996,7 +59993,7 @@
         <v>케이위드</v>
       </c>
       <c r="E78" s="93" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F78" s="94">
         <v>74</v>
@@ -60094,7 +60091,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E79" s="93" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F79" s="94">
         <v>75</v>
@@ -60192,7 +60189,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E80" s="93" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F80" s="94">
         <v>76</v>
@@ -60290,7 +60287,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E81" s="93" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F81" s="94">
         <v>77</v>
@@ -60388,7 +60385,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E82" s="93" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F82" s="94">
         <v>78</v>
@@ -60486,7 +60483,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E83" s="93" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F83" s="94">
         <v>79</v>
@@ -60584,7 +60581,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E84" s="93" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F84" s="94">
         <v>80</v>
@@ -60682,7 +60679,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E85" s="93" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F85" s="94">
         <v>81</v>
@@ -60780,7 +60777,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E86" s="93" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F86" s="94">
         <v>82</v>
@@ -60881,7 +60878,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E87" s="93" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F87" s="94">
         <v>83</v>
@@ -60979,7 +60976,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E88" s="93" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F88" s="94">
         <v>84</v>
@@ -61077,7 +61074,7 @@
         <v>케이위드</v>
       </c>
       <c r="E89" s="106" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F89" s="94">
         <v>85</v>
@@ -61175,7 +61172,7 @@
         <v>케이위드</v>
       </c>
       <c r="E90" s="93" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F90" s="94">
         <v>86</v>
@@ -61273,7 +61270,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E91" s="93" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F91" s="94">
         <v>87</v>
@@ -61371,7 +61368,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E92" s="93" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F92" s="94">
         <v>88</v>
@@ -61472,7 +61469,7 @@
         <v>케이위드</v>
       </c>
       <c r="E93" s="93" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F93" s="94">
         <v>89</v>
@@ -61570,7 +61567,7 @@
         <v>케이위드</v>
       </c>
       <c r="E94" s="93" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F94" s="94">
         <v>90</v>
@@ -61668,7 +61665,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E95" s="93" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F95" s="94">
         <v>91</v>
@@ -61766,7 +61763,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E96" s="93" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F96" s="94">
         <v>92</v>
@@ -61864,7 +61861,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E97" s="93" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F97" s="94">
         <v>93</v>
@@ -61962,7 +61959,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E98" s="93" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F98" s="94">
         <v>94</v>
@@ -62060,7 +62057,7 @@
         <v>케이위드</v>
       </c>
       <c r="E99" s="93" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F99" s="94">
         <v>95</v>
@@ -62158,7 +62155,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E100" s="93" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F100" s="94">
         <v>96</v>
@@ -62255,7 +62252,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E101" s="93" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F101" s="94">
         <v>97</v>
@@ -62352,7 +62349,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E102" s="93" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F102" s="94">
         <v>98</v>
@@ -62449,7 +62446,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E103" s="93" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F103" s="94">
         <v>99</v>
@@ -62546,7 +62543,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E104" s="93" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F104" s="94">
         <v>100</v>
@@ -62646,7 +62643,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E105" s="93" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F105" s="94">
         <v>101</v>
@@ -62746,7 +62743,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E106" s="93" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F106" s="94">
         <v>102</v>
@@ -62846,7 +62843,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E107" s="93" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F107" s="94">
         <v>103</v>
@@ -62946,7 +62943,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E108" s="93" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F108" s="94">
         <v>104</v>
@@ -63046,7 +63043,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E109" s="93" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F109" s="94">
         <v>105</v>
@@ -63146,7 +63143,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E110" s="93" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F110" s="94">
         <v>106</v>
@@ -63246,7 +63243,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E111" s="93" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F111" s="94">
         <v>107</v>
@@ -63343,7 +63340,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E112" s="93" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F112" s="94">
         <v>108</v>
@@ -63440,7 +63437,7 @@
         <v>제이더블유엘</v>
       </c>
       <c r="E113" s="93" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F113" s="94">
         <v>109</v>
@@ -63537,7 +63534,7 @@
         <v>0</v>
       </c>
       <c r="E114" s="93" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F114" s="94">
         <v>110</v>
@@ -63633,7 +63630,7 @@
         <v>0</v>
       </c>
       <c r="E115" s="93" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F115" s="94">
         <v>111</v>
@@ -63729,7 +63726,7 @@
         <v>0</v>
       </c>
       <c r="E116" s="93" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F116" s="94">
         <v>112</v>
@@ -63825,7 +63822,7 @@
         <v>0</v>
       </c>
       <c r="E117" s="106" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F117" s="94">
         <v>113</v>
@@ -63921,7 +63918,7 @@
         <v>0</v>
       </c>
       <c r="E118" s="93" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F118" s="94">
         <v>114</v>
@@ -64017,7 +64014,7 @@
         <v>0</v>
       </c>
       <c r="E119" s="93" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F119" s="94">
         <v>115</v>
@@ -64113,7 +64110,7 @@
         <v>0</v>
       </c>
       <c r="E120" s="93" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F120" s="94">
         <v>116</v>
@@ -64209,7 +64206,7 @@
         <v>0</v>
       </c>
       <c r="E121" s="93" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F121" s="94">
         <v>117</v>
@@ -64305,7 +64302,7 @@
         <v>0</v>
       </c>
       <c r="E122" s="93" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F122" s="94">
         <v>118</v>
@@ -64401,7 +64398,7 @@
         <v>0</v>
       </c>
       <c r="E123" s="93" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F123" s="94">
         <v>119</v>
@@ -64497,7 +64494,7 @@
         <v>0</v>
       </c>
       <c r="E124" s="93" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F124" s="94">
         <v>120</v>
@@ -64593,7 +64590,7 @@
         <v>0</v>
       </c>
       <c r="E125" s="93" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F125" s="94">
         <v>121</v>
@@ -64689,7 +64686,7 @@
         <v>0</v>
       </c>
       <c r="E126" s="93" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F126" s="94">
         <v>122</v>
@@ -64785,7 +64782,7 @@
         <v>0</v>
       </c>
       <c r="E127" s="93" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F127" s="94">
         <v>123</v>
@@ -64881,7 +64878,7 @@
         <v>0</v>
       </c>
       <c r="E128" s="93" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F128" s="94">
         <v>124</v>
@@ -64977,7 +64974,7 @@
         <v>0</v>
       </c>
       <c r="E129" s="93" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F129" s="94">
         <v>125</v>
@@ -65073,7 +65070,7 @@
         <v>0</v>
       </c>
       <c r="E130" s="93" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F130" s="94">
         <v>126</v>
@@ -65169,7 +65166,7 @@
         <v>0</v>
       </c>
       <c r="E131" s="93" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F131" s="94">
         <v>127</v>
@@ -65265,7 +65262,7 @@
         <v>0</v>
       </c>
       <c r="E132" s="93" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F132" s="94">
         <v>128</v>
@@ -65361,7 +65358,7 @@
         <v>0</v>
       </c>
       <c r="E133" s="93" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F133" s="108">
         <v>129</v>
@@ -65457,7 +65454,7 @@
         <v>0</v>
       </c>
       <c r="E134" s="93" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F134" s="108">
         <v>130</v>
@@ -65557,7 +65554,7 @@
         <v>0</v>
       </c>
       <c r="E135" s="93" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F135" s="108">
         <v>131</v>
@@ -65654,7 +65651,7 @@
         <v>0</v>
       </c>
       <c r="E136" s="93" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F136" s="108">
         <v>132</v>
@@ -65751,7 +65748,7 @@
         <v>0</v>
       </c>
       <c r="E137" s="93" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F137" s="108">
         <v>133</v>
@@ -65848,7 +65845,7 @@
         <v>0</v>
       </c>
       <c r="E138" s="93" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F138" s="108">
         <v>134</v>
@@ -65945,7 +65942,7 @@
         <v>0</v>
       </c>
       <c r="E139" s="93" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F139" s="108">
         <v>135</v>
@@ -66042,7 +66039,7 @@
         <v>0</v>
       </c>
       <c r="E140" s="93" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F140" s="108">
         <v>136</v>
@@ -66139,7 +66136,7 @@
         <v>0</v>
       </c>
       <c r="E141" s="79" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F141" s="108">
         <v>137</v>
@@ -66236,7 +66233,7 @@
         <v>0</v>
       </c>
       <c r="E142" s="79" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F142" s="108">
         <v>138</v>
@@ -66333,7 +66330,7 @@
         <v>0</v>
       </c>
       <c r="E143" s="79" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F143" s="108">
         <v>139</v>
@@ -66430,7 +66427,7 @@
         <v>0</v>
       </c>
       <c r="E144" s="79" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F144" s="108">
         <v>140</v>
@@ -66527,7 +66524,7 @@
         <v>0</v>
       </c>
       <c r="E145" s="79" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F145" s="108">
         <v>141</v>
@@ -66624,7 +66621,7 @@
         <v>0</v>
       </c>
       <c r="E146" s="79" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F146" s="108">
         <v>142</v>
@@ -66721,7 +66718,7 @@
         <v>0</v>
       </c>
       <c r="E147" s="79" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F147" s="108">
         <v>143</v>
@@ -66818,7 +66815,7 @@
         <v>0</v>
       </c>
       <c r="E148" s="79" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F148" s="108">
         <v>144</v>
@@ -66915,7 +66912,7 @@
         <v>0</v>
       </c>
       <c r="E149" s="79" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F149" s="108">
         <v>145</v>
@@ -69521,7 +69518,7 @@
       <c r="Y178" s="118"/>
       <c r="Z178" s="78"/>
       <c r="AB178" s="126" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AC178" s="127">
         <f>AD176</f>
@@ -69596,7 +69593,7 @@
       <c r="Y179" s="118"/>
       <c r="Z179" s="78"/>
       <c r="AB179" s="129" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AC179" s="130">
         <f>AC178*0.1</f>
@@ -69671,7 +69668,7 @@
       <c r="Y180" s="118"/>
       <c r="Z180" s="78"/>
       <c r="AB180" s="133" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AC180" s="134">
         <f>SUM(AC178:AD179)</f>
@@ -70002,7 +69999,7 @@
       <c r="W193" s="119"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="30">
     <mergeCell ref="F1:U2"/>
     <mergeCell ref="AB1:AD2"/>
     <mergeCell ref="V1:V2"/>
@@ -70019,8 +70016,6 @@
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
-    <mergeCell ref="S3:S4"/>
-    <mergeCell ref="T3:T4"/>
     <mergeCell ref="U3:U4"/>
     <mergeCell ref="V3:V4"/>
     <mergeCell ref="W3:W4"/>
